--- a/IT8106 Ubiquitous Computing and Intelligent Systems/assignment 1/IT8106_IoT_Paper_Matrix.xlsx
+++ b/IT8106 Ubiquitous Computing and Intelligent Systems/assignment 1/IT8106_IoT_Paper_Matrix.xlsx
@@ -1241,7 +1241,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1249,7 +1249,7 @@
     <col width="42" customWidth="1" min="3" max="3"/>
     <col width="36" customWidth="1" min="4" max="4"/>
     <col width="42" customWidth="1" min="5" max="5"/>
-    <col width="78" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
     <col width="24" customWidth="1" min="7" max="7"/>
     <col width="36" customWidth="1" min="8" max="8"/>
     <col width="52" customWidth="1" min="9" max="9"/>
@@ -1283,20 +1283,25 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Abstract (verbatim)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Conclusion</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Methodology</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Role in your report</t>
         </is>
@@ -1305,47 +1310,50 @@
     <row r="2" ht="160" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>sensors-23-07927-2.pdf</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+          <t>energies-19-00965-with-cover.pdf</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Intelligent ADL Recognition via IoT-Based Multimodal Deep Learning Framework</t>
+          <t>A Survey on IoT-Based Smart Electrical Systems: An Analysis of Standards, Security, and Applications</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Madiha Javeed; Naif Al Mudawi; Abdulwahab Alazeb; Sultan Almakdi; Saud S. Alotaibi; Samia Allaoua Chelloug; Ahmad Jalal</t>
+          <t>Chiara Matta; Sara Pinna; Samoel Ortu; Francesco Parodo; Daniele Giusto; Matteo Anedda</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Sensors, vol. 23, no. 18, article 7927, 2023. doi 10.3390/s23187927. Received 25 Jul 2023, accepted 13 Sep 2023, published 16 Sep 2023. Air University Islamabad + Najran University + Umm Al-Qura University + Princess Nourah bint Abdulrahman University. Open access (CC BY 4.0).</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Smart home monitoring systems via internet of things (IoT) are required for taking care of elders at home. They provide the flexibility of monitoring elders remotely for their families and caregivers. Activities of daily living are an efficient way to effectively monitor elderly people at home and patients at caregiving facilities. The monitoring of such actions depends largely on IoT-based devices, either wireless or installed at different places. This paper proposes an effective and robust layered architecture using multisensory devices to recognize the activities of daily living from anywhere. Multimodality refers to the sensory devices of multiple types working together to achieve the objective of remote monitoring. Therefore, the proposed multimodal-based approach includes IoT devices, such as wearable inertial sensors and videos recorded during daily routines, fused together. The data from these multi-sensors have to be processed through a pre-processing layer through different stages, such as data filtration, segmentation, landmark detection, and 2D stick model. In the next layer, called the features processing, we have extracted, fused, and optimized different features from multimodal sensors. The final layer, called classification, has been utilized to recognize the activities of daily living via a deep learning technique known as convolutional neural network. It is observed from the proposed IoT-based multimodal layered system's results that an acceptable mean accuracy rate of 84.14% has been achieved.</t>
-        </is>
+          <t>Energies, vol. 19, no. 4, article 965, 2026. doi 10.3390/en19040965. University of Cagliari (Italy) + Dauvea srl. Open access (CC BY 4.0).</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2026</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Our proposed method for IoT-based ADL recognition is an important novel idea for the elderly home monitoring system. It is a combination of multimodal-based sensors to compute the ADL recognition efficiently. Mean accuracies of 84.12% and 84.17% have been achieved over Opportunity++ and Berkeley-MHAD datasets. The results have shown that the proposed ADL recognition technique has outperformed other state-of-the-art methodologies. In the future the authors will focus on privacy issues and improving the 2D stick model, and note the system currently removes background from videos captured by immobile indoor cameras, so it may not generalise to different background settings.</t>
+          <t>The rapid integration of Internet of Things (IoT) technologies is transforming electrical power systems into intelligent, interconnected, and data-driven infrastructures, enabling advanced monitoring, control, and optimization across the entire energy value chain. This paper delivers a comprehensive survey that systematically analyzes and interrelates nine key dimensions that prior literature largely examines in separate silos: architectural models, communication protocols, reference standards, cybersecurity and privacy mechanisms, data processing paradigms (edge, fog, and cloud), interoperability solutions, energy management strategies, application scenarios, and future research directions. Unlike conventional reviews confined to single-layer or domain-specific perspectives, this survey adopts a holistic, cross-layer approach, explicitly linking architectural choices, protocol stacks, interoperability frameworks, and security mechanisms with application and energy management requirements.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Layered IoT architecture (pre-processing -&gt; feature processing -&gt; classification) fusing wearable inertial sensor data and video; CNN-based classification; experimental evaluation reaching 84.14% mean accuracy.</t>
+          <t>No single short-range (Wi-Fi/ZigBee/BLE/Z-Wave) or long-range (LoRaWAN/NB-IoT/Sigfox) standard dominates - each trades energy efficiency, latency and range differently, so protocol choice must match the application. IT/OT interoperability (bridging IoT protocols like MQTT/CoAP with grid protocols like IEC 61850) and layered security (encryption, IDS, differential privacy) remain open challenges; the authors identify scalable IT/OT security, real-time edge AI, and semantic standard harmonisation as the three biggest research gaps going forward.</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Backs your Section 3 (Heterogeneity / Distributed Intelligence) and Section 4 general framing - a real layered architecture combining wearable + a second sensor type mirrors your own multi-device design. Useful precedent for justifying why SmartBuild fuses several device categories rather than relying on one.</t>
+          <t>PRISMA-guided systematic literature review of ~1200 initial records (Google Scholar/MDPI/IEEE/ScienceDirect) narrowed to 100 studies; cross-layer taxonomy linking IoT architecture layers, short/long-range communication protocols (Wi-Fi, ZigBee, BLE, Z-Wave, LoRaWAN, NB-IoT, Sigfox), commercial vs open-source smart-home platforms, EMS/AI optimisation approaches, and security threat/countermeasure taxonomy (NIST-aligned).</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Provides a broad protocol/security backbone reference for the whole household system rather than an elderly-specific one - its short-range protocol comparison (Wi-Fi/ZigBee/BLE/Z-Wave) and security-threat taxonomy (DoS, FDI, eavesdropping, MitM) support the report's core network/security-protocol section, applicable to the household as a whole with elderly monitoring cited as one downstream use case.</t>
         </is>
       </c>
     </row>
@@ -1375,31 +1383,34 @@
           <t>Sensors, vol. 25, no. 3, article 853, 2025. doi 10.3390/s25030853. Received 19 Nov 2024, accepted 24 Jan 2025, published 30 Jan 2025. University College London. Open access (CC BY 4.0).</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>The integration of IoT and Ambient Assisted Living (AAL) enables discreet real-time health monitoring in home environments, offering significant potential for personalized and preventative care. However, challenges persist in balancing privacy, cost, usability, and system reliability. This paper provides an overview of recent advancements in sensor and IoT technologies for assisted living, with a focus on elderly individuals living independently. It categorizes sensor types and technologies that enhance healthcare delivery and explores an interdisciplinary framework encompassing sensing, communication, and decision-making systems. Through this analysis, this paper highlights current applications, identifies emerging challenges, and pinpoints critical areas for future research. This paper aims to inform ongoing discourse and advocate for interdisciplinary approaches in system design to address existing trade-offs and optimize performance.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>This article provides an overview of current and emerging AAL solutions across three key domains: sensors, communications, and decision making, and explores the interdisciplinary challenges that emerge when developing such solutions, including privacy, performance, cost and usability. Strategies like edge computing for immediate analysis and cloud storage for long-term trends, supported by AI algorithms, can optimize data management without compromising privacy or efficiency. Future research must prioritize standardization of protocols and interoperability across healthcare platforms, and address data ownership and privacy through a holistic approach spanning IoT, sensing, security, AI and control systems.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
         <is>
           <t>Literature review / categorization of sensor types and technologies into an interdisciplinary sensing-communication-decision-making framework, with a trade-off analysis (privacy, cost, usability, reliability).</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Backs the general framing of your whole Section 4 - its sensor categorisation lines up closely with your wearable/sound/motion/CSI subsections, and its privacy-cost-usability-reliability trade-off framing is directly usable in Section 5 Recommendations.</t>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Supports the report's general sensing-technology framing across the household (sensor categorisation into wearable/ambient/environmental) rather than being elderly-specific; its privacy-cost-usability-reliability trade-off model is directly reusable in the Recommendations section for justifying design choices for the household system as a whole.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="160" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2311.09248v1-2.pdf</t>
+          <t>HSR2-8-e70498.pdf</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1409,44 +1420,47 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Smart Home Goal Feature Model - A guide to support Smart Homes for Ageing in Place</t>
+          <t>IoT-Based Elderly Health Monitoring System Using Firebase Cloud Computing</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Irini Logothetis; Priya Rani; Shangeetha Sivasothy; Rajesh Vasa; Kon Mouzakis</t>
+          <t>Adhan Efendi; Muhammad Imam Ammarullah; Indra Griha Tofik Isa; Meli Puspita Sari; Jasmine Nurul Izza; Yohanes Sinung Nugroho; Hamid Nasrullah; Denny Alfian</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2311.09248v1, 2023. Applied Artificial Intelligence Institute, Deakin University + School of Engineering, RMIT University.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Smart technologies are significant in supporting ageing in place for elderly. Leveraging Artificial Intelligence (AI) and Machine Learning (ML), it provides peace of mind, enabling the elderly to continue living independently. Elderly use smart technologies for entertainment and social interactions, this can be extended to provide safety and monitor health and environmental conditions, detect emergencies and notify informal and formal caregivers when care is needed. This paper provides an overview of the smart home technologies commercially available to support ageing in place, the advantages and challenges of smart home technologies, and their usability from elderly's perspective. Synthesizing prior knowledge, we created a structured Smart Home Goal Feature Model (SHGFM) to resolve heuristic approaches used by the Subject Matter Experts (SMEs) at aged care facilities and healthcare researchers in adapting smart homes. The SHGFM provides SMEs the ability to (i) establish goals and (ii) identify features to set up strategies to design, develop and deploy smart homes for the elderly based on personalised needs. Our model provides guidance to healthcare researchers and aged care industries to set up smart homes based on the needs of elderly, by defining a set of goals at different levels mapped to a different set of features.</t>
-        </is>
+          <t>Health Science Reports, vol. 8, article e70498, 2025. doi 10.1002/hsr2.70498. Received 18 Jul 2024, revised 9 Jan 2025, accepted 5 Feb 2025, published 2 Mar 2025. Open access (CC BY).</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>This paper synthesises the knowledge in smart home technologies supporting ageing in place into a structured Smart Home Goal Feature Model (SHGFM), providing a tool SMEs can use to identify the level of smart home support an elderly person needs based on case-by-case assessment. Previous research indicates current holistic approaches to smart home systems for the elderly result in low adoption, often due to poor interface design, privacy and trust issues, and economic or educational barriers. The SHGFM resolves this by defining a set of goals at different levels mapped to a corresponding set of features, guiding healthcare researchers and aged care industries in designing, developing and deploying smart homes based on personalised elderly needs.</t>
+          <t>Background and Aims: The increasing elderly population presents significant challenges for healthcare systems, necessitating innovative solutions for continuous health monitoring. This study develops and validates an IoT-based elderly monitoring system designed to enhance the quality of life for elderly people. The system features a robust Android-based user interface integrated with the Firebase cloud platform, ensuring real-time data collection and analysis. In addition, a supervised machine learning technology is implemented to conduct prediction task of the observed user whether in "stable" or "not stable" condition based on real-time parameter. Methods: The system architecture adopts the IoT layer including physical layer, network layer, and application layer. Device validation is conducted by involving six participants to measure the real-time data of heart-rate, oxygen saturation, and body temperature, then analysed by mean average percentage error (MAPE) to define error rate. A comparative experiment is conducted to define the optimal supervised machine learning model to be deployed into the system by analysing evaluation metrics. Meanwhile, the user satisfaction aspect evaluated by the terms of usability, comfort, security, and effectiveness. Results: IoT-based elderly health monitoring system has been constructed with a MAPE of 0.90% across the parameters: heart-rate (1.68%), oxygen saturation (0.57%), and body temperature (0.44%). In machine learning experiment indicates XGBoost model has the optimal performance based on the evaluation metrics of accuracy and F1 score which generates 0.973 and 0.970, respectively. In user satisfaction aspect based on usability, comfort, security, and effectiveness achieving a high rating of 86.55%.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Literature synthesis + design of a structured Smart Home Goal Feature Model (SHGFM) mapping elderly-care goals to smart home features.</t>
+          <t>This system offers practical applications for both elderly users and caregivers, enabling real-time monitoring of health conditions. Future enhancements may include integration with artificial intelligence technologies such as machine learning and deep learning to predict health conditions from data patterns, further improving the system's capabilities and effectiveness in elderly care.</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Backs your Introduction and Section 5 Recommendations - its goal-to-feature mapping approach parallels your own device-to-need justification (e.g. why Samsung Galaxy Watch, why Zigbee for stationary sensors, why WiFi CSI/BLE for presence and broadcast).</t>
+          <t>System design/development using a 3-layer IoT architecture (physical/network/application) + device validation with 6 participants (MAPE error analysis) + comparative ML experiment (XGBoost best performer) + user satisfaction survey.</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Serves as one concrete use-case example under the household system's elderly-care module - its 3-layer IoT architecture (physical/network/application) is reusable for the report's general architecture section, while the ML-based health-status prediction illustrates how the same architecture supports a specific care use case.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="160" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>HSR2-8-e70498.pdf</t>
+          <t>2509.18411v1.pdf</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1456,44 +1470,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>IoT-Based Elderly Health Monitoring System Using Firebase Cloud Computing</t>
+          <t>LIFY: IoT System for Monitoring Vital Signs of Elderly People</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Adhan Efendi; Muhammad Imam Ammarullah; Indra Griha Tofik Isa; Meli Puspita Sari; Jasmine Nurul Izza; Yohanes Sinung Nugroho; Hamid Nasrullah; Denny Alfian</t>
+          <t>S. Gonzalez; M. Vasquez; W. Castellanos</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Health Science Reports, vol. 8, article e70498, 2025. doi 10.1002/hsr2.70498. Received 18 Jul 2024, revised 9 Jan 2025, accepted 5 Feb 2025, published 2 Mar 2025. Open access (CC BY).</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Background and Aims: The increasing elderly population presents significant challenges for healthcare systems, necessitating innovative solutions for continuous health monitoring. This study develops and validates an IoT-based elderly monitoring system designed to enhance the quality of life for elderly people. The system features a robust Android-based user interface integrated with the Firebase cloud platform, ensuring real-time data collection and analysis. In addition, a supervised machine learning technology is implemented to conduct prediction task of the observed user whether in "stable" or "not stable" condition based on real-time parameter. Methods: The system architecture adopts the IoT layer including physical layer, network layer, and application layer. Device validation is conducted by involving six participants to measure the real-time data of heart-rate, oxygen saturation, and body temperature, then analysed by mean average percentage error (MAPE) to define error rate. A comparative experiment is conducted to define the optimal supervised machine learning model to be deployed into the system by analysing evaluation metrics. Meanwhile, the user satisfaction aspect evaluated by the terms of usability, comfort, security, and effectiveness. Results: IoT-based elderly health monitoring system has been constructed with a MAPE of 0.90% across the parameters: heart-rate (1.68%), oxygen saturation (0.57%), and body temperature (0.44%). In machine learning experiment indicates XGBoost model has the optimal performance based on the evaluation metrics of accuracy and F1 score which generates 0.973 and 0.970, respectively. In user satisfaction aspect based on usability, comfort, security, and effectiveness achieving a high rating of 86.55%.</t>
-        </is>
+          <t>arXiv:2509.18411v1, 2025. Pontificia Universidad Javeriana, Bogota, Colombia (Electronic Engineering + ARTICO research group + e-TEAM ecosystem for emerging technologies for older adults).</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>This system offers practical applications for both elderly users and caregivers, enabling real-time monitoring of health conditions. Future enhancements may include integration with artificial intelligence technologies such as machine learning and deep learning to predict health conditions from data patterns, further improving the system's capabilities and effectiveness in elderly care.</t>
+          <t>This article describes the implementation of a technological solution aimed at improving the recording of physiological signals in the elderly population residing in geriatric facilities. The developed system consists of a smart device equipped with sensors for body temperature, heart rate, and blood oxygen levels. This device establishes an Internet connection to transmit data to a cloud-based platform for storage. Within this platform, a dashboard has been created to visualize real-time values captured by the sensors, along with additional functionalities such as user management and the configuration of personalized alerts, which are transmitted to the solution's users through the instant messaging system called Telegram.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>System design/development using a 3-layer IoT architecture (physical/network/application) + device validation with 6 participants (MAPE error analysis) + comparative ML experiment (XGBoost best performer) + user satisfaction survey.</t>
+          <t>This project stands out for its focus on implementing IoT technologies for monitoring the health of the elderly population, with a personalised automatic alarm system tailored to each patient's needs that reduces the risk of complications and provides reassurance to patients, caregivers and families. A key contribution is the ability to access information about the elderly from anywhere via any internet-connected device, including direct alert messages sent to family members through Telegram. The project's focus on cost efficiency, using low-cost components like the Raspberry Pi plus free Firebase and ThingsBoard platforms, makes it highly affordable and accessible compared to similar, often expensive, solutions.</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 4's general architecture framing - its physical/network/application layer structure lines up with your protocol comparison (4.6), and its ML-based 'stable/not stable' prediction is a good citation for extending your alert-tier logic in Section 5 Recommendations.</t>
+          <t>System implementation - smart wearable device (temperature, heart rate, SpO2 sensors) + cloud dashboard + configurable personalised alerts delivered via Telegram.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>An elderly-care use-case precedent within the broader household system - its configurable, tiered alert design (temperature/heart rate/SpO2) is evidence that alert customisation is an established pattern applicable to any monitored occupant, not just elderly residents, and can back the report's general alerting/escalation logic.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="160" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>2509.18411v1.pdf</t>
+          <t>sensors-25-05252.pdf</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1503,44 +1520,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>LIFY: IoT System for Monitoring Vital Signs of Elderly People</t>
+          <t>Stage-Wise IoT Solutions for Alzheimer's Disease: A Systematic Review of Detection, Monitoring, and Assistive Technologies</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>S. Gonzalez; M. Vasquez; W. Castellanos</t>
+          <t>Sanket Salvi; Lalit Garg; Varadraj Gurupur</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2509.18411v1, 2025. Pontificia Universidad Javeriana, Bogota, Colombia (Electronic Engineering + ARTICO research group + e-TEAM ecosystem for emerging technologies for older adults).</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>This article describes the implementation of a technological solution aimed at improving the recording of physiological signals in the elderly population residing in geriatric facilities. The developed system consists of a smart device equipped with sensors for body temperature, heart rate, and blood oxygen levels. This device establishes an Internet connection to transmit data to a cloud-based platform for storage. Within this platform, a dashboard has been created to visualize real-time values captured by the sensors, along with additional functionalities such as user management and the configuration of personalized alerts, which are transmitted to the solution's users through the instant messaging system called Telegram.</t>
-        </is>
+          <t>Sensors, vol. 25, article 5252, 2025. doi 10.3390/s25175252. Received 12 Jun 2025, accepted 21 Aug 2025, published 23 Aug 2025. University of Central Florida + University of Malta. Open access (CC BY 4.0).</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>This project stands out for its focus on implementing IoT technologies for monitoring the health of the elderly population, with a personalised automatic alarm system tailored to each patient's needs that reduces the risk of complications and provides reassurance to patients, caregivers and families. A key contribution is the ability to access information about the elderly from anywhere via any internet-connected device, including direct alert messages sent to family members through Telegram. The project's focus on cost efficiency, using low-cost components like the Raspberry Pi plus free Firebase and ThingsBoard platforms, makes it highly affordable and accessible compared to similar, often expensive, solutions.</t>
+          <t>The Internet of Things (IoT) has emerged as a transformative technology in managing Alzheimer's Disease (AD), offering novel solutions for early diagnosis, continuous patient monitoring, and assistive care. This review presents a comprehensive analysis of IoT-enabled systems tailored to AD care, focusing on wearable biosensors, cognitive monitoring tools, smart home automation, and Artificial Intelligence (AI)-driven analytics. A systematic literature survey was conducted using the Preferred Reporting Items for Systematic Reviews and Meta-Analyses (PRISMA) guidelines to identify, screen, and synthesize 236 relevant studies primarily published between 2020 and 2025 across IEEE Xplore, PubMed, Scopus and Web of Science. The inclusion criteria targeted peer-reviewed articles that proposed or evaluated IoT-based solutions for AD detection, progression monitoring, or patient assistance. It systematically investigates how IoT innovations facilitate early diagnosis, disease management, and patient supervision, ultimately aiming to improve care quality and support caregivers. The paper categorizes IoT applications into three primary intervention stages: Early detection, utilizing cognitive assessment tools and wearable sensors; Mild-stage management, including remote monitoring, memory aids, and fall detection systems; Severe-stage care, involving smart home automation, medication adherence systems, and patient safety through location tracking solutions. Key enabling IoT technologies analyzed in the review encompass wearable biosensors, ambient intelligent smart home systems, AI-driven predictive analytics, cloud-based healthcare solutions, and existing data security frameworks. Moreover, the effectiveness of monitoring techniques and gaps in the current research landscape are systematically presented and discussed.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>System implementation - smart wearable device (temperature, heart rate, SpO2 sensors) + cloud dashboard + configurable personalised alerts delivered via Telegram.</t>
+          <t>This PRISMA-guided review of 236 studies presents a stage-wise synthesis of IoT and AI interventions in Alzheimer's disease: early detection (wearable IMUs for gait, smartphone/video cognitive self-assessments, multimodal deep learning, &gt;90% accuracy in controlled settings, but short, single-site and underpowered evaluations), mild-stage management (remote monitoring detecting falls/agitation with sensitivities typically &gt;90%, though larger trials are needed), and severe-stage care (smart home anomaly detection, medication adherence up to 95% on-time, GPS/IMU wandering detection &gt;90% accuracy, mostly still at pilot/proof-of-concept stage). Systemic challenges include privacy/security risk, immature interoperability standardisation, unclear regulatory pathways, algorithmic bias, unequal access in low- and middle-income countries, and ethical issues around data sovereignty and consent.</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>Backs your Use Case 1 three-tier alert concept (Section 2.1) - a real deployed example of configurable personalised alerts sent to caregivers, useful evidence that tiered/configurable alerting is an established pattern, not just your own invention.</t>
+          <t>PRISMA-guided systematic literature review of 236 studies (2020-2025) across IEEE Xplore, PubMed, Scopus and Web of Science.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Elderly/dementia-specific use case supporting the household system's health-monitoring module; useful evidence base for the Introduction to motivate why elderly care is one of several household needs the system addresses, without positioning it as the system's sole purpose.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="160" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>sensors-25-05252.pdf</t>
+          <t>sensors-25-03341.pdf</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1550,279 +1570,297 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Stage-Wise IoT Solutions for Alzheimer's Disease: A Systematic Review of Detection, Monitoring, and Assistive Technologies</t>
+          <t>Machine Learning-Based Security Solutions for IoT Networks: A Comprehensive Survey</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Sanket Salvi; Lalit Garg; Varadraj Gurupur</t>
+          <t>Abdullah Alfahaid; Easa Alalwany; Abdulqader M. Almars; Fatemah Alharbi; Elsayed Atlam; Imad Mahgoub</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Sensors, vol. 25, article 5252, 2025. doi 10.3390/s25175252. Received 12 Jun 2025, accepted 21 Aug 2025, published 23 Aug 2025. University of Central Florida + University of Malta. Open access (CC BY 4.0).</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>The Internet of Things (IoT) has emerged as a transformative technology in managing Alzheimer's Disease (AD), offering novel solutions for early diagnosis, continuous patient monitoring, and assistive care. This review presents a comprehensive analysis of IoT-enabled systems tailored to AD care, focusing on wearable biosensors, cognitive monitoring tools, smart home automation, and Artificial Intelligence (AI)-driven analytics. A systematic literature survey was conducted using the Preferred Reporting Items for Systematic Reviews and Meta-Analyses (PRISMA) guidelines to identify, screen, and synthesize 236 relevant studies primarily published between 2020 and 2025 across IEEE Xplore, PubMed, Scopus and Web of Science. The inclusion criteria targeted peer-reviewed articles that proposed or evaluated IoT-based solutions for AD detection, progression monitoring, or patient assistance. It systematically investigates how IoT innovations facilitate early diagnosis, disease management, and patient supervision, ultimately aiming to improve care quality and support caregivers. The paper categorizes IoT applications into three primary intervention stages: Early detection, utilizing cognitive assessment tools and wearable sensors; Mild-stage management, including remote monitoring, memory aids, and fall detection systems; Severe-stage care, involving smart home automation, medication adherence systems, and patient safety through location tracking solutions. Key enabling IoT technologies analyzed in the review encompass wearable biosensors, ambient intelligent smart home systems, AI-driven predictive analytics, cloud-based healthcare solutions, and existing data security frameworks. Moreover, the effectiveness of monitoring techniques and gaps in the current research landscape are systematically presented and discussed.</t>
-        </is>
+          <t>Sensors, vol. 25, article 3341, 2025. doi 10.3390/s25113341. Received 4 Mar 2025, accepted 22 May 2025, published 26 May 2025. Taibah University + Florida Atlantic University. Open access (CC BY 4.0).</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>This PRISMA-guided review of 236 studies presents a stage-wise synthesis of IoT and AI interventions in Alzheimer's disease: early detection (wearable IMUs for gait, smartphone/video cognitive self-assessments, multimodal deep learning, &gt;90% accuracy in controlled settings, but short, single-site and underpowered evaluations), mild-stage management (remote monitoring detecting falls/agitation with sensitivities typically &gt;90%, though larger trials are needed), and severe-stage care (smart home anomaly detection, medication adherence up to 95% on-time, GPS/IMU wandering detection &gt;90% accuracy, mostly still at pilot/proof-of-concept stage). Systemic challenges include privacy/security risk, immature interoperability standardisation, unclear regulatory pathways, algorithmic bias, unequal access in low- and middle-income countries, and ethical issues around data sovereignty and consent.</t>
+          <t>The Internet of Things (IoT) is revolutionizing industries by enabling seamless interconnectivity across domains such as healthcare, smart cities, the Industrial Internet of Things (IIoT), and the Internet of Vehicles (IoV). However, IoT security remains a significant challenge due to vulnerabilities related to data breaches, privacy concerns, cyber threats, and trust management issues. Addressing these risks requires advanced security mechanisms, with machine learning (ML) emerging as a powerful tool for anomaly detection, intrusion detection, and threat mitigation. This survey provides a comprehensive review of ML-driven IoT security solutions from 2020 to 2024, examining the effectiveness of supervised, unsupervised, and reinforcement learning approaches, as well as advanced techniques such as deep learning (DL), ensemble learning (EL), federated learning (FL), and transfer learning (TL). A systematic classification of ML techniques is presented based on their IoT security applications, along with a taxonomy of security threats and a critical evaluation of existing solutions in terms of scalability, computational efficiency, and privacy preservation. Additionally, this study identifies key limitations of current ML approaches, including high computational costs, adversarial vulnerabilities, and interpretability challenges, while outlining future research opportunities such as privacy-preserving ML, explainable AI, and edge-based security frameworks. By synthesizing insights from recent advancements, this paper provides a structured framework for developing robust, intelligent, and adaptive IoT security solutions.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>PRISMA-guided systematic literature review of 236 studies (2020-2025) across IEEE Xplore, PubMed, Scopus and Web of Science.</t>
+          <t>The IoT is a transformative paradigm interconnecting devices across transportation, healthcare, industry and urban management, but increasing reliance on it raises critical challenges around security, privacy and trust. ML is a fundamental enabler of IoT security, with supervised, unsupervised and reinforcement learning, deep learning, ensemble learning, federated learning and transfer learning all improving real-time threat detection, mitigating cyberattacks and enhancing privacy protection across domains including smart cities, healthcare, IIoT and IoV. Persistent challenges remain, including high computational costs, scalability limitations, adversarial vulnerabilities and the need for more interpretable ML models, with future research prioritising adaptive, scalable, explainable intrusion detection systems.</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 4 broadly across every device category (wearables, smart home automation, location tracking, security) - a large, recent evidence base. Also useful for your Introduction to motivate elderly-focused IoT generally, beyond just fall detection.</t>
+          <t>Comprehensive literature survey (2020-2024) + systematic classification/taxonomy of ML-based IoT security techniques and threats.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Core security-protocol evidence for the household system as a whole (not elderly-specific) - supports the report's network security/intrusion-detection discussion for the shared home gateway and sensor network, since any occupant's data (health, presence, security) flowing through the system needs the same ML-based anomaly-detection safeguards.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="160" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5.ETECHE24_finalIqra.pdf</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+          <t>sensors-25-02638.pdf</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Multi-Modal Sensors Fusion for Fall Detection and Action Recognition in Indoor Environment</t>
+          <t>Occupancy Monitoring Using BLE Beacons: Intelligent Bluetooth Virtual Door System</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Iqra Aijaz Abro; Ahmad Jalal</t>
+          <t>Nasrettin Koksal; AbdulRahman Ghannoum; William Melek; Patricia Nieva</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Presented at ETECHE 2024. Dept. of Computer Science, Air University, Islamabad, Pakistan.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>In computer vision and inertial sensors, recent research focuses on monitoring and identifying falls, as well as daily actions, through autonomous human action detection. In this paper, the proposed model utilizes multi-modal sensors for fall detection. The data from inertial sensors was filtered using a bilateral filter, known for its monotonic and maximum flat magnitude response in the passband, giving smoothness. Key properties, such as the Gaussian Mixture Model (GMM) and parseval's energy, were retrieved. Additionally, fall detection was accomplished utilizing RGB (red-green-blue) videos, where features such as rectangles, triangles, full-body ridges, and full-body curves were generated. The final results from the inertial sensor and vision data were fused utilizing multimodal fusion. We then optimized the fused data using the Naive Bayes approach and trained Multi-layer perceptron (MLP) classifier for classification. The UR Fall Detection (URFD) dataset was utilized to evaluate the proposed system, demonstrating its usefulness by reaching an accuracy of 88%.</t>
-        </is>
+          <t>Sensors, vol. 25, no. 9, article 2638, 2025. doi 10.3390/s25092638. Received 10 Mar 2025, accepted 13 Apr 2025, published 22 Apr 2025. University of Waterloo (Canada) + Qatar University. Open access (CC BY 4.0).</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>In this paper the authors built a multimodal fall detection system based on vision and inertial data and achieved 88% accuracy on the URFD dataset, across seven phases including data preprocessing, feature extraction, and classification via an MLP classifier. Visual data offers body and geometry features while inertial sensors provide GMM and energy features, and combining them increases accuracy over either modality alone. Challenges include light and noise sensitivity; future work aims to add deep learning classifiers for better temporal recognition and incorporate depth and heat sensors to overcome occlusion and inadequate lighting.</t>
+          <t>Occupancy monitoring (OM) and the localization of individuals within indoor environments using wearable devices offer a very promising data communication solution in applications such as home automation, smart office management, outbreak monitoring, and emergency operating plans. OM is challenging when developing solutions that focus on reduced power consumption and cost. Bluetooth low energy (BLE) technology is energy- and cost-efficient compared to other technologies. Integrating BLE Received Signal Strength Indicator (RSSI) signals with machine learning (ML) introduces a new Artificial Intelligence- (AI-) enhanced OM approach. In this paper, we propose an Intelligent Bluetooth Virtual Door (IBVD) OM system for the indoor/outdoor tracking of individuals using the interaction between a BLE device worn by the occupant and two BLE beacons located at the entrance/exit points of a doorway. ML algorithms are used to perform intelligent OM through pattern detection from the BLE RSSI signal(s). This approach differs from other technologies in that it does not require any floorplan information. The developed OM system achieves a range between 96.6% and 97.3% classification accuracy for all tested ML models, where the error translates to a minor delay in the time in which an individual's location is classified, introducing a highly reliable indoor/outdoor tracking system.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Multi-modal sensor fusion (inertial sensors + RGB video) + Naive Bayes feature optimization + MLP classification; evaluated on the URFD dataset, 88% accuracy.</t>
+          <t>The IBVD system, using two BLE beacons forming a 'virtual door' and RNN-based ML models (LSTM, GRU, hybrid), achieves 96.6-97.3% indoor/outdoor classification accuracy without needing any floorplan knowledge, and requires no dedicated positioning hardware. The hybrid model gave the best generalisation in k-fold validation. The authors note the system is designed to scale to multi-room deployments and note future work on multi-occupant, obstacle-rich environments and interference from neighbouring BLE systems.</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>STRONG MATCH. Directly backs your Use Case 1 cross-verification logic (Section 2.1) - real evidence that fusing more than one sensor type improves fall-detection reliability over any single sensor. Good citation for why your fall trigger requires wearable + sound + motion + WiFi CSI agreement rather than one device alone.</t>
+          <t>Two BLE beacons (K8, BLE 5.0) mounted either side of a doorway with Faraday shielding to sharpen the RSSI transition; a BLE wearable target device (TraceSCAN) broadcasts an anonymous ID; RSSI-only features (no floorplan) fed into LSTM/GRU/hybrid RNNs; 48 scripted entry/exit scenarios x 5 trials (240 datasets, ~105,000 datapoints), evaluated via confusion matrix and 4-fold cross-validation.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Directly supports the household system's core occupancy/access-monitoring capability - a low-cost, floorplan-free BLE 'virtual door' works for any household member, with elderly-resident room-entry/exit tracking being one specific application rather than the paper's sole relevance.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="160" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>sensors-25-03341.pdf</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+          <t>sensors-25-02205.pdf</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning-Based Security Solutions for IoT Networks: A Comprehensive Survey</t>
+          <t>A Decade of Progress in Wearable Sensors for Fall Detection (2015-2024): A Network-Based Visualization Review</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Abdullah Alfahaid; Easa Alalwany; Abdulqader M. Almars; Fatemah Alharbi; Elsayed Atlam; Imad Mahgoub</t>
+          <t>Yifei Li; Pei Liu; Yan Fang; Xiangyuan Wu; Yewei Xie; Zhongzhi Xu; Hao Ren; Fengshi Jing</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>Sensors, vol. 25, article 3341, 2025. doi 10.3390/s25113341. Received 4 Mar 2025, accepted 22 May 2025, published 26 May 2025. Taibah University + Florida Atlantic University. Open access (CC BY 4.0).</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>The Internet of Things (IoT) is revolutionizing industries by enabling seamless interconnectivity across domains such as healthcare, smart cities, the Industrial Internet of Things (IIoT), and the Internet of Vehicles (IoV). However, IoT security remains a significant challenge due to vulnerabilities related to data breaches, privacy concerns, cyber threats, and trust management issues. Addressing these risks requires advanced security mechanisms, with machine learning (ML) emerging as a powerful tool for anomaly detection, intrusion detection, and threat mitigation. This survey provides a comprehensive review of ML-driven IoT security solutions from 2020 to 2024, examining the effectiveness of supervised, unsupervised, and reinforcement learning approaches, as well as advanced techniques such as deep learning (DL), ensemble learning (EL), federated learning (FL), and transfer learning (TL). A systematic classification of ML techniques is presented based on their IoT security applications, along with a taxonomy of security threats and a critical evaluation of existing solutions in terms of scalability, computational efficiency, and privacy preservation. Additionally, this study identifies key limitations of current ML approaches, including high computational costs, adversarial vulnerabilities, and interpretability challenges, while outlining future research opportunities such as privacy-preserving ML, explainable AI, and edge-based security frameworks. By synthesizing insights from recent advancements, this paper provides a structured framework for developing robust, intelligent, and adaptive IoT security solutions.</t>
-        </is>
+          <t>Sensors, vol. 25, no. 7, article 2205, 2025. Hikvision Research Institute + Zhejiang University + City University of Macau + Duke-NUS + Sun Yat-sen University + Jinan University + UNC Chapel Hill.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>The IoT is a transformative paradigm interconnecting devices across transportation, healthcare, industry and urban management, but increasing reliance on it raises critical challenges around security, privacy and trust. ML is a fundamental enabler of IoT security, with supervised, unsupervised and reinforcement learning, deep learning, ensemble learning, federated learning and transfer learning all improving real-time threat detection, mitigating cyberattacks and enhancing privacy protection across domains including smart cities, healthcare, IIoT and IoV. Persistent challenges remain, including high computational costs, scalability limitations, adversarial vulnerabilities and the need for more interpretable ML models, with future research prioritising adaptive, scalable, explainable intrusion detection systems.</t>
+          <t>Over the past decade, wearable sensors for fall detection have gained significant attention due to their potential in improving the safety of elderly users and reducing fall-related injuries. This review employs a network-based visualization approach to analyze research trends, key technologies, and collaborative networks. Using studies from SCI- and SSCI-indexed journals from 2015 to 2024, we analyzed 582 articles and 65 reviews with CiteSpace, revealing a significant rise in research on wearable sensors for fall detection. Additionally, we reviewed various datasets and machine learning techniques, from traditional methods to advanced deep learning frameworks, which demonstrate high accuracies, F1 scores, sensitivities, and specificities in controlled testing.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Comprehensive literature survey (2020-2024) + systematic classification/taxonomy of ML-based IoT security techniques and threats.</t>
+          <t>Wearable-sensor fall-detection research has grown steadily and diversified from simple accelerometer thresholding to deep learning frameworks with high reported accuracy in lab conditions. The authors note this is one of the first systematic bibliometric surveys of review papers (rather than primary studies) in this space, and call out cost, comfort, privacy and real-world (vs. lab) predictive reliability as the persistent open challenges that must be addressed for wearable fall-detection sensors to fulfil their potential in elderly care.</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Backs Section 4.5 (security mode / smart lock) - justifies the anomaly and intrusion-detection framing behind your escalation logic (unresolved alarm -&gt; local security/police). Useful for discussing why a sensor network handling emergency data needs security safeguards beyond basic encryption.</t>
+          <t>Bibliometric/network-based visualization review using CiteSpace over 582 articles and 65 review papers (SCI/SSCI-indexed, 2015-2024), mapping research trends, key technologies, datasets and ML techniques (traditional to deep learning) and collaboration networks in wearable fall-detection research.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-focused use-case evidence within the household system's health-monitoring module; gives citable trend data on wearable fall-detection research to frame why the system includes a multi-sensor elderly-care component alongside its broader household security capabilities.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="160" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>engproc-76-00085-with-cover.pdf</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
+          <t>healthcare-13-02066.pdf</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>IoT-Based Smart Remote Door Lock and Monitoring System Using an Android Application</t>
+          <t>Wearable Devices &amp; Elderly: A Bibliometric Analysis of 2014-2024</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Jakia Sultana Sonamoni; Raihan Sikdar; A. S. M. Ahsanul Sarkar Akib; Md Shamiul Islam; Salahin Sourov; Md Abdullah Al Ahasan; Mahadir Islam; Md Ahsan Habib; M. F. Mridha</t>
+          <t>Haojun Zhi; Mariia Zolotova</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Engineering Proceedings, vol. 76, no. 1, article 85, 2024. doi 10.3390/engproc2024076085. Presented at ICIMP-2024, Regina, Canada, 27-29 Jun 2024. Published 19 Nov 2024. Open access (CC BY 4.0).</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Nowadays, it is very important to secure our home perfectly. To make our life easier and more secure, we are presenting our smart door lock system project. We implement an IoT-based smart door lock system using an ESP32-CAM and an Android application in this project. Most of the time in our daily life, we forget to lock our doors and later we suffer from confusion about whether we locked all doors perfectly or not. In this project, we implement a smart door lock system, by which the owner can see the visitor's picture and then lock or unlock their doors from anywhere and at any time using the Android application. Whenever visitors come to visit the home and press the doorbell, the owner will receive a notification on his/her smartphone and then the owner can see the visitor's picture by using the Android app. After checking the visitor, the owner can let them enter the house by unlocking the door remotely. If the door is locked perfectly, then the door lock signal in the application will show a green signal. If the door is not locked perfectly, the signal will show red and then the owner can remotely lock their door easily from anywhere. In this project, we have also utilized a theft alert. If anyone comes in front of the door and tries to enter the house forcefully then a theft alert notification will be sent to the owner's smartphone and a Buzzer Alert will ring in the house loudly so that the neighbors can be aware of the theft and can take action. The automatic door lock feature is also available in this system.</t>
-        </is>
+          <t>Healthcare, vol. 13, no. 16, article 2066, 2025. doi:10.3390/healthcare13162066. Xi'an Jiaotong-Liverpool University + University of Liverpool.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>2025</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>The IoT-based Smart Remote Door Lock and Monitoring System with an Android app improves home security, although it has limitations and room for development. Internet access is crucial to the system's remote operation and can be unstable or unavailable, and facial recognition for visitor identification may be inaccurate in poor lighting or with concealed features. Integration with other smart home devices may introduce compatibility issues and vulnerabilities, necessitating strong cybersecurity. Future work could add offline functions for critical operations, optimise facial recognition accuracy, and continue cybersecurity and data-encryption research to protect user privacy and system integrity.</t>
+          <t>Background: The ageing population demands effective health solutions for the elderly. Wearable devices offer real-time monitoring and early alerts, but a comprehensive review of research in this field is lacking. This study uses bibliometric methods to analyse trends and advances in wearable devices for the elderly. Methods: Literature from 2014 to 2024 was retrieved from the Web of Science Core Collection using keywords related to the elderly and wearable devices. A total of 1015 English-language papers were analysed using tools including CiteSpace, VOSviewer, and R-Bibliometrix. Results: The annual growth rate of publications was 7.65%, with research increasing from 4 in 2014 to 1015 in 2024. Major contributors were the United States and China. Research shifted from fall detection and activity monitoring to heart rate variability, balance, and AI integration. Conclusions: Research on wearable devices for the elderly is growing rapidly. Future studies should focus on multimodal sensor fusion, AI-enhanced analytics and personalised health interventions, and long-term, real-world validation of wearable solutions to improve elderly health management.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Hardware-software system design (ESP32-CAM + Android app) + implementation and demonstration of remote lock/unlock, visitor notification and a theft-alert buzzer.</t>
+          <t>The field has matured from foundational fall-detection/activity-monitoring work into sophisticated, AI-integrated systems, but two systemic barriers dominate: technology-adoption factors (usability, affordability, trust, self-efficacy) and infrastructural gaps - especially lack of interoperability between devices/healthcare systems and persistent data privacy/security concerns. The authors recommend future work prioritise multimodal sensor fusion, AI-enhanced analytics, personalised interventions and long-term real-world (not just lab) validation.</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Directly backs Section 4.5 smart lock evaluation - its theft-alert buzzer notifying neighbours is a close real-world precedent for your BLE neighbour-broadcast concept. Good citation to sit alongside the August/Eufy/TP-Link entries in your smart lock comparison table.</t>
+          <t>Bibliometric analysis of 1015 English-language Web of Science papers (2014-2024) using CiteSpace, VOSviewer and R-Bibliometrix to map publication growth, leading contributors/authors (Bijan Najafi, Lynn Rochester), and thematic evolution (fall detection -&gt; heart rate variability, balance, AI integration).</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care use-case evidence - its finding that interoperability and privacy/trust are the top non-technical adoption barriers is directly citable for the household system's overall privacy-by-design and BLE-interoperability rationale, relevant across all household functions, not only elderly monitoring.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="160" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>sensors-25-02638.pdf</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
+          <t>5.ETECHE24_finalIqra.pdf</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Occupancy Monitoring Using BLE Beacons: Intelligent Bluetooth Virtual Door System</t>
+          <t>Multi-Modal Sensors Fusion for Fall Detection and Action Recognition in Indoor Environment</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Nasrettin Koksal; AbdulRahman Ghannoum; William Melek; Patricia Nieva</t>
+          <t>Iqra Aijaz Abro; Ahmad Jalal</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Sensors, vol. 25, no. 9, article 2638, 2025. doi 10.3390/s25092638. Received 10 Mar 2025, accepted 13 Apr 2025, published 22 Apr 2025. University of Waterloo (Canada) + Qatar University. Open access (CC BY 4.0).</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Occupancy monitoring (OM) and the localization of individuals within indoor environments using wearable devices offer a very promising data communication solution in applications such as home automation, smart office management, outbreak monitoring, and emergency operating plans. OM is challenging when developing solutions that focus on reduced power consumption and cost. Bluetooth low energy (BLE) technology is energy- and cost-efficient compared to other technologies. Integrating BLE Received Signal Strength Indicator (RSSI) signals with machine learning (ML) introduces a new Artificial Intelligence- (AI-) enhanced OM approach. In this paper, we propose an Intelligent Bluetooth Virtual Door (IBVD) OM system for the indoor/outdoor tracking of individuals using the interaction between a BLE device worn by the occupant and two BLE beacons located at the entrance/exit points of a doorway. ML algorithms are used to perform intelligent OM through pattern detection from the BLE RSSI signal(s). This approach differs from other technologies in that it does not require any floorplan information. The developed OM system achieves a range between 96.6% and 97.3% classification accuracy for all tested ML models, where the error translates to a minor delay in the time in which an individual's location is classified, introducing a highly reliable indoor/outdoor tracking system.</t>
-        </is>
+          <t>Presented at ETECHE 2024. Dept. of Computer Science, Air University, Islamabad, Pakistan.</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>The IBVD system, using two BLE beacons forming a 'virtual door' and RNN-based ML models (LSTM, GRU, hybrid), achieves 96.6-97.3% indoor/outdoor classification accuracy without needing any floorplan knowledge, and requires no dedicated positioning hardware. The hybrid model gave the best generalisation in k-fold validation. The authors note the system is designed to scale to multi-room deployments and note future work on multi-occupant, obstacle-rich environments and interference from neighbouring BLE systems.</t>
+          <t>In computer vision and inertial sensors, recent research focuses on monitoring and identifying falls, as well as daily actions, through autonomous human action detection. In this paper, the proposed model utilizes multi-modal sensors for fall detection. The data from inertial sensors was filtered using a bilateral filter, known for its monotonic and maximum flat magnitude response in the passband, giving smoothness. Key properties, such as the Gaussian Mixture Model (GMM) and parseval's energy, were retrieved. Additionally, fall detection was accomplished utilizing RGB (red-green-blue) videos, where features such as rectangles, triangles, full-body ridges, and full-body curves were generated. The final results from the inertial sensor and vision data were fused utilizing multimodal fusion. We then optimized the fused data using the Naive Bayes approach and trained Multi-layer perceptron (MLP) classifier for classification. The UR Fall Detection (URFD) dataset was utilized to evaluate the proposed system, demonstrating its usefulness by reaching an accuracy of 88%.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Two BLE beacons (K8, BLE 5.0) mounted either side of a doorway with Faraday shielding to sharpen the RSSI transition; a BLE wearable target device (TraceSCAN) broadcasts an anonymous ID; RSSI-only features (no floorplan) fed into LSTM/GRU/hybrid RNNs; 48 scripted entry/exit scenarios x 5 trials (240 datasets, ~105,000 datapoints), evaluated via confusion matrix and 4-fold cross-validation.</t>
+          <t>In this paper the authors built a multimodal fall detection system based on vision and inertial data and achieved 88% accuracy on the URFD dataset, across seven phases including data preprocessing, feature extraction, and classification via an MLP classifier. Visual data offers body and geometry features while inertial sensors provide GMM and energy features, and combining them increases accuracy over either modality alone. Challenges include light and noise sensitivity; future work aims to add deep learning classifiers for better temporal recognition and incorporate depth and heat sensors to overcome occlusion and inadequate lighting.</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Directly supports the BLE and occupancy-monitoring strand of SmartBuild - a low-cost, floorplan-free 'virtual door' design is a strong precedent for room-entry/exit tracking of an elderly resident without cameras, and demonstrates BLE's cost/power advantage over PIR, ultrasonic, WiFi and camera-based occupancy sensing discussed elsewhere in your report.</t>
+          <t>Multi-modal sensor fusion (inertial sensors + RGB video) + Naive Bayes feature optimization + MLP classification; evaluated on the URFD dataset, 88% accuracy.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Supports the household system's general sensor-fusion design principle (used across security, occupancy and elderly health-monitoring functions) - real evidence that combining sensor types improves detection reliability, applicable to the system's fall-detection use case as one instance of this broader design pattern.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="160" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Real-Time_Indoor_Localization_System_Based_on_Wear.pdf</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+          <t>engproc-76-00085-with-cover.pdf</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Real-Time Indoor Localization System Based on Wearable Device, Bluetooth Low Energy (BLE) Beacons, and Machine Learning</t>
+          <t>IoT-Based Smart Remote Door Lock and Monitoring System Using an Android Application</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Baejah; Nur Ahmadi; Rahmat Mulyawan; Trio Adiono</t>
+          <t>Jakia Sultana Sonamoni; Raihan Sikdar; A. S. M. Ahsanul Sarkar Akib; Md Shamiul Islam; Salahin Sourov; Md Abdullah Al Ahasan; Mahadir Islam; Md Ahsan Habib; M. F. Mridha</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access, vol. 11/12, 2024. doi 10.1109/ACCESS.2024.3490608. Bandung Institute of Technology (ITB), Indonesia.</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Indoor localization systems are critical in various domains, particularly healthcare, where real-time monitoring of elderly and dementia patients is essential. Current systems face significant challenges in achieving both high accuracy and real-time performance in indoor environments. To address this issue, this study proposes an accurate and real-time indoor localization system that integrates Bluetooth Low Energy (BLE) beacons, wearable device, and advanced machine learning algorithm to enhance room-level localization accuracy. We explored and optimized six machine learning models, including XGBoost, LightGBM, Random Forest, K-Nearest Neighbor (KNN), Support Vector Machine (SVM), and Multilayer Perceptron (MLP). A Bayesian optimization framework, Optuna, was used to optimize the hyperparameters of machine learning models. Received Signal Strength Indicator (RSSI) data from 15 participants across 10 rooms were collected and processed for performance evaluation and comparison. Based on the experimental results, XGBoost emerged as the highest performing model, with an average accuracy, precision, recall, and F1-score of 0.91. The complete system demonstrates real-time capability, with an end-to-end execution time of 1,346.27 ms. This highlights the system's potential for practical, accurate, and real-time indoor localization.</t>
-        </is>
+          <t>Engineering Proceedings, vol. 76, no. 1, article 85, 2024. doi 10.3390/engproc2024076085. Presented at ICIMP-2024, Regina, Canada, 27-29 Jun 2024. Published 19 Nov 2024. Open access (CC BY 4.0).</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>XGBoost was the best-performing of six ML models for room-level BLE localization (0.91 accuracy/precision/recall/F1), and the full ESP32-to-Raspberry-Pi pipeline meets a 1-1.5s real-time response requirement at 1.35s end-to-end. The paper is explicitly motivated by Indonesia's rising dementia burden and elderly falls, and the authors note class imbalance (room size differences) as a limitation, suggesting data augmentation/oversampling as future work.</t>
+          <t>Nowadays, it is very important to secure our home perfectly. To make our life easier and more secure, we are presenting our smart door lock system project. We implement an IoT-based smart door lock system using an ESP32-CAM and an Android application in this project. Most of the time in our daily life, we forget to lock our doors and later we suffer from confusion about whether we locked all doors perfectly or not. In this project, we implement a smart door lock system, by which the owner can see the visitor's picture and then lock or unlock their doors from anywhere and at any time using the Android application. Whenever visitors come to visit the home and press the doorbell, the owner will receive a notification on his/her smartphone and then the owner can see the visitor's picture by using the Android app. After checking the visitor, the owner can let them enter the house by unlocking the door remotely. If the door is locked perfectly, then the door lock signal in the application will show a green signal. If the door is not locked perfectly, the signal will show red and then the owner can remotely lock their door easily from anywhere. In this project, we have also utilized a theft alert. If anyone comes in front of the door and tries to enter the house forcefully then a theft alert notification will be sent to the owner's smartphone and a Buzzer Alert will ring in the house loudly so that the neighbors can be aware of the theft and can take action. The automatic door lock feature is also available in this system.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10 BLE beacons (iBKS 105) fixed per room, RSSI captured by an ESP32-based wearable Base Station Node; six ML classifiers (XGBoost, LightGBM, Random Forest, KNN, SVM, MLP) tuned via Optuna Bayesian optimization; 80/10/10 train/val/test split on ~12,358 cleaned samples from 15 participants across 10 rooms; end-to-end real-time deployment measured on ESP32 + Raspberry Pi 4.</t>
+          <t>The IoT-based Smart Remote Door Lock and Monitoring System with an Android app improves home security, although it has limitations and room for development. Internet access is crucial to the system's remote operation and can be unstable or unavailable, and facial recognition for visitor identification may be inaccurate in poor lighting or with concealed features. Integration with other smart home devices may introduce compatibility issues and vulnerabilities, necessitating strong cybersecurity. Future work could add offline functions for critical operations, optimise facial recognition accuracy, and continue cybersecurity and data-encryption research to protect user privacy and system integrity.</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>Strong direct match to SmartBuild's elderly-monitoring and room-level localization goals - explicitly frames BLE+wearable+ML indoor localization as a dementia/fall-risk safety tool, and gives a concrete real-time latency benchmark (1.35s) you can cite when justifying your own system's responsiveness requirements.</t>
+          <t>Hardware-software system design (ESP32-CAM + Android app) + implementation and demonstration of remote lock/unlock, visitor notification and a theft-alert buzzer.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Core household-security use case - a smart door lock with theft-alert notification is a direct precedent for the system's entry-security function, protecting the household generally; its Android-app remote control and neighbour-alert concept support the report's central security-protocol design regardless of elderly occupancy.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="160" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Journal of Electrical and Computer Engineering - 2024 - Abdul Salam.pdf</t>
+          <t>Real-Time_Indoor_Localization_System_Based_on_Wear.pdf</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1832,44 +1870,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>An Overview of Recent Wireless Technologies for IoT-Enabled Smart Grids</t>
+          <t>Real-Time Indoor Localization System Based on Wearable Device, Bluetooth Low Energy (BLE) Beacons, and Machine Learning</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Rashiqa Abdul Salam; Naeem Iqbal Ratyal; Ubaid Ahmed; Imran Aziz; Muhammad Sajid; Anzar Mahmood</t>
+          <t>Baejah; Nur Ahmadi; Rahmat Mulyawan; Trio Adiono</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Wiley Journal of Electrical and Computer Engineering, vol. 2024, Article ID 2568751, 22 pages, 2024. doi 10.1155/jece/2568751. Mirpur University of Science and Technology (Pakistan) + Uppsala University (Sweden). Open access.</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Smart Grid is a way of providing bidirectional energy flow with the integration of latest communication technologies and advanced control methods to overcome the issues associated with the current power grid such as unidirectional power flow, resource wastage, reliability, security, enhanced quality, and increasing demand of energy. Integrating Internet of Things (IoTs) makes Smart Grid hyperaware and agile to enhance the efficiency, reliability, and sustainability of electricity distribution. This study comprehensively reviews various wireless technologies for IoT-enabled Smart Grids that could be integrated into home area networks (HANs), neighborhood area networks (NANs), and wide-area networks (WANs), comparing them in terms of data rates, range, adaptability, internet protocol support and other parameters. IoT technologies, including ZigBee, Z-wave, Bluetooth, Wi-Fi, NFC, 6LoWPAN, wireless HART, and Thread, are suggested for operations in HANs; for NANs and WANs, LTE, WiMax and LPWAN are explored. The study further analyzes applications and challenges of IoT-enabled Smart Grids.</t>
-        </is>
+          <t>IEEE Access, vol. 11/12, 2024. doi 10.1109/ACCESS.2024.3490608. Bandung Institute of Technology (ITB), Indonesia.</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>ZigBee and Z-wave offer similar low data rates/range/power with ZigBee supporting more nodes; Bluetooth 5.0 is secure and now IPv6-capable; Wi-Fi gives high data rates/long range but suffers interference; for wide-area use, LoRaWAN/SigFox/Neul trade off range, power and latency against LTE/WiMax's higher cost but greater reliability. The authors conclude no single wireless standard is universally best - the right choice depends on the specific HAN/NAN/WAN application context.</t>
+          <t>Indoor localization systems are critical in various domains, particularly healthcare, where real-time monitoring of elderly and dementia patients is essential. Current systems face significant challenges in achieving both high accuracy and real-time performance in indoor environments. To address this issue, this study proposes an accurate and real-time indoor localization system that integrates Bluetooth Low Energy (BLE) beacons, wearable device, and advanced machine learning algorithm to enhance room-level localization accuracy. We explored and optimized six machine learning models, including XGBoost, LightGBM, Random Forest, K-Nearest Neighbor (KNN), Support Vector Machine (SVM), and Multilayer Perceptron (MLP). A Bayesian optimization framework, Optuna, was used to optimize the hyperparameters of machine learning models. Received Signal Strength Indicator (RSSI) data from 15 participants across 10 rooms were collected and processed for performance evaluation and comparison. Based on the experimental results, XGBoost emerged as the highest performing model, with an average accuracy, precision, recall, and F1-score of 0.91. The complete system demonstrates real-time capability, with an end-to-end execution time of 1,346.27 ms. This highlights the system's potential for practical, accurate, and real-time indoor localization.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>Literature review/comparative-analysis methodology across 8 short-range and 5 long-range wireless standards (ZigBee, Z-Wave, Bluetooth/BLE, Wi-Fi, 6LoWPAN, Thread, Wireless HART, NFC, LTE, LoRaWAN, SigFox, Neul, WiMax), summarised in comparison tables of data rate, range, cost, latency and adoption.</t>
+          <t>XGBoost was the best-performing of six ML models for room-level BLE localization (0.91 accuracy/precision/recall/F1), and the full ESP32-to-Raspberry-Pi pipeline meets a 1-1.5s real-time response requirement at 1.35s end-to-end. The paper is explicitly motivated by Indonesia's rising dementia burden and elderly falls, and the authors note class imbalance (room size differences) as a limitation, suggesting data augmentation/oversampling as future work.</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>Lower direct relevance (smart-grid rather than elderly-care focus), but its side-by-side comparison of ZigBee/Z-Wave/Wi-Fi/Bluetooth/6LoWPAN/Thread data rate, range, power and latency is reusable background evidence when your report justifies choosing BLE over alternative protocols for SmartBuild's home-area network.</t>
+          <t>10 BLE beacons (iBKS 105) fixed per room, RSSI captured by an ESP32-based wearable Base Station Node; six ML classifiers (XGBoost, LightGBM, Random Forest, KNN, SVM, MLP) tuned via Optuna Bayesian optimization; 80/10/10 train/val/test split on ~12,358 cleaned samples from 15 participants across 10 rooms; end-to-end real-time deployment measured on ESP32 + Raspberry Pi 4.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Core occupant-localisation capability for the household system - BLE+wearable+ML room-level tracking is motivated by elderly/dementia care in this paper but is architecturally general-purpose, supporting the report's broader indoor-localisation design used for both security (intruder/occupant tracking) and elderly-care use cases.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="160" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>energies-19-00965-with-cover.pdf</t>
+          <t>Journal of Electrical and Computer Engineering - 2024 - Abdul Salam.pdf</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1879,37 +1920,40 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>A Survey on IoT-Based Smart Electrical Systems: An Analysis of Standards, Security, and Applications</t>
+          <t>An Overview of Recent Wireless Technologies for IoT-Enabled Smart Grids</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Chiara Matta; Sara Pinna; Samoel Ortu; Francesco Parodo; Daniele Giusto; Matteo Anedda</t>
+          <t>Rashiqa Abdul Salam; Naeem Iqbal Ratyal; Ubaid Ahmed; Imran Aziz; Muhammad Sajid; Anzar Mahmood</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Energies, vol. 19, no. 4, article 965, 2026. doi 10.3390/en19040965. University of Cagliari (Italy) + Dauvea srl. Open access (CC BY 4.0).</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>The rapid integration of Internet of Things (IoT) technologies is transforming electrical power systems into intelligent, interconnected, and data-driven infrastructures, enabling advanced monitoring, control, and optimization across the entire energy value chain. This paper delivers a comprehensive survey that systematically analyzes and interrelates nine key dimensions that prior literature largely examines in separate silos: architectural models, communication protocols, reference standards, cybersecurity and privacy mechanisms, data processing paradigms (edge, fog, and cloud), interoperability solutions, energy management strategies, application scenarios, and future research directions. Unlike conventional reviews confined to single-layer or domain-specific perspectives, this survey adopts a holistic, cross-layer approach, explicitly linking architectural choices, protocol stacks, interoperability frameworks, and security mechanisms with application and energy management requirements.</t>
-        </is>
+          <t>Wiley Journal of Electrical and Computer Engineering, vol. 2024, Article ID 2568751, 22 pages, 2024. doi 10.1155/jece/2568751. Mirpur University of Science and Technology (Pakistan) + Uppsala University (Sweden). Open access.</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>No single short-range (Wi-Fi/ZigBee/BLE/Z-Wave) or long-range (LoRaWAN/NB-IoT/Sigfox) standard dominates - each trades energy efficiency, latency and range differently, so protocol choice must match the application. IT/OT interoperability (bridging IoT protocols like MQTT/CoAP with grid protocols like IEC 61850) and layered security (encryption, IDS, differential privacy) remain open challenges; the authors identify scalable IT/OT security, real-time edge AI, and semantic standard harmonisation as the three biggest research gaps going forward.</t>
+          <t>Smart Grid is a way of providing bidirectional energy flow with the integration of latest communication technologies and advanced control methods to overcome the issues associated with the current power grid such as unidirectional power flow, resource wastage, reliability, security, enhanced quality, and increasing demand of energy. Integrating Internet of Things (IoTs) makes Smart Grid hyperaware and agile to enhance the efficiency, reliability, and sustainability of electricity distribution. This study comprehensively reviews various wireless technologies for IoT-enabled Smart Grids that could be integrated into home area networks (HANs), neighborhood area networks (NANs), and wide-area networks (WANs), comparing them in terms of data rates, range, adaptability, internet protocol support and other parameters. IoT technologies, including ZigBee, Z-wave, Bluetooth, Wi-Fi, NFC, 6LoWPAN, wireless HART, and Thread, are suggested for operations in HANs; for NANs and WANs, LTE, WiMax and LPWAN are explored. The study further analyzes applications and challenges of IoT-enabled Smart Grids.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>PRISMA-guided systematic literature review of ~1200 initial records (Google Scholar/MDPI/IEEE/ScienceDirect) narrowed to 100 studies; cross-layer taxonomy linking IoT architecture layers, short/long-range communication protocols (Wi-Fi, ZigBee, BLE, Z-Wave, LoRaWAN, NB-IoT, Sigfox), commercial vs open-source smart-home platforms, EMS/AI optimisation approaches, and security threat/countermeasure taxonomy (NIST-aligned).</t>
+          <t>ZigBee and Z-wave offer similar low data rates/range/power with ZigBee supporting more nodes; Bluetooth 5.0 is secure and now IPv6-capable; Wi-Fi gives high data rates/long range but suffers interference; for wide-area use, LoRaWAN/SigFox/Neul trade off range, power and latency against LTE/WiMax's higher cost but greater reliability. The authors conclude no single wireless standard is universally best - the right choice depends on the specific HAN/NAN/WAN application context.</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Lower direct relevance (smart-grid/building energy focus rather than elderly health), but Table 2/5's short-range protocol comparison (power consumption, data rate, topology for Wi-Fi/ZigBee/BLE/Z-Wave) and its security-threat taxonomy (DoS, FDI, eavesdropping, MitM with matching countermeasures) are reusable for SmartBuild's privacy/security discussion around home-area BLE networks.</t>
+          <t>Literature review/comparative-analysis methodology across 8 short-range and 5 long-range wireless standards (ZigBee, Z-Wave, Bluetooth/BLE, Wi-Fi, 6LoWPAN, Thread, Wireless HART, NFC, LTE, LoRaWAN, SigFox, Neul, WiMax), summarised in comparison tables of data rate, range, cost, latency and adoption.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>Background protocol-comparison evidence for the household system's network design (lower elderly relevance) - its data-rate/range/power comparison of ZigBee/Z-Wave/Wi-Fi/BLE/Thread supports justifying protocol choice for the whole home-area network.</t>
         </is>
       </c>
     </row>
@@ -1939,31 +1983,34 @@
           <t>IEEE Transactions on Wireless Communications, accepted 2024. arXiv:2307.12126v2 [cs.IT]. Samsung Research America, Standards and Mobility Innovation Lab.</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>Due to its ubiquitous and contact-free nature, the use of WiFi infrastructure for performing sensing tasks has tremendous potential. However, the channel state information (CSI) measured by a WiFi receiver suffers from errors in both its gain and phase, which can significantly hinder sensing tasks. By analyzing these errors from different WiFi receivers, a mathematical model for these gain and phase errors is developed in this work. Based on these models, several theoretically justified preprocessing algorithms for correcting such errors at a receiver and thus obtaining clean CSI are presented. Simulation results show that the developed algorithms for cleaning CSI can reduce noise by 40% and 200%, respectively, compared to baseline methods for gain correction and phase correction, without significantly impacting computational cost. The superiority of the proposed methods is also validated in a real-world test bed for respiration rate monitoring (an example sensing task), where they improve the estimation signal-to-noise ratio by 20% compared to baseline methods.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>The proposed maximum-likelihood-based gain and phase correction algorithms outperform heuristic baselines by 40% and 200%, respectively, in simulation, and improve real-world respiration-rate estimation SNR by 20%, without materially increasing computation time. The authors note that when the sensing signal is very weak (static-channel fraction &gt; 0.95), simply ignoring CSI power variation performs best - a useful nuance for practitioners.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="I15" s="2" t="inlineStr">
         <is>
           <t>Mathematical modelling of WiFi CSI gain error (large-scale + AGC components) and timing/common-phase-error, validated against two real-world WiFi test beds (Intel AX210, Broadcom BCM4358); several ML/least-squares correction algorithms proposed and benchmarked against baselines over 2000 simulated channel realisations and a 75-episode real-world respiration-monitoring test bed.</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>Relevant as a non-BLE, contact-free sensing alternative for SmartBuild's health-monitoring discussion - demonstrates WiFi CSI can track something as fine-grained as breathing rate without wearables, useful when comparing device-free WiFi sensing against your BLE wearable approach for vital-sign or presence monitoring.</t>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>Core device-free sensing technique for the household system (general-purpose, not elderly-specific) - demonstrates WiFi CSI can track vital signs like respiration without wearables, supporting the report's broader device-free sensing strand used across occupancy, security and health-monitoring functions.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="160" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>2304.13107v2.pdf</t>
+          <t>PIR_Sensor-Based_Occupancy_Monitoring_in_Smart_Bui.pdf</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1973,44 +2020,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Time-Selective RNN for Device-Free Multi-Room Human Presence Detection Using WiFi CSI</t>
+          <t>PIR Sensor-Based Occupancy Monitoring in Smart Buildings: A Review of Methodologies and Machine Learning Approaches</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Li-Hsiang Shen; An-Hung Hsiao; Fang-Yu Chu; Kai-Ten Feng</t>
+          <t>Azad Shokrollahi; Jan Persson; Reza Malekian; Arezoo Sarkheyli-Hägele; Fredrik Karlsson</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2304.13107v2 [cs.AI], 2023. National Central University + National Yang Ming Chiao Tung University (NYCU), Taiwan.</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Device-free human presence detection is a crucial technology for various applications, including home automation, security, and healthcare. While camera-based systems have traditionally been used for this purpose, they raise privacy concerns. To address this issue, recent research has explored the use of wireless channel state information (CSI) extracted from commercial WiFi access points (APs). In this paper, we propose a device-free human presence detection system for multi-room scenarios using a time-selective conditional dual feature extract recurrent network (TCD-FERN). Our system captures significant time features using a dynamic and static data preprocessing technique, extracting both moving and spatial features and differentiating between line-of-sight (LoS) and non-line-of-sight (NLoS) cases. A voting scheme is adopted to mitigate the feature attenuation problem caused by room partitions, with around 3% improvement of human presence detection accuracy. Compared to existing works, our proposed TCD-FERN system can achieve above 97% of human presence detection accuracy for multi-room scenarios with the adoption of fewer WiFi APs.</t>
-        </is>
+          <t>Preprints.org, posted 29 Jan 2024, doi:10.20944/preprints202401.1924.v1 (not peer-reviewed preprint). Malmö University (Sweden) + Sony Network Communications.</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>TCD-FERN achieves over 97% multi-room presence detection accuracy using only one WiFi AP per room (a star topology transmitter-in-centre design), substantially outperforming existing benchmarks (R-TTWD, HARNN) by roughly 20-40%. Detection is notably harder for the transmitter's own room due to signal attenuation through walls, which the proposed voting scheme improves by up to ~12 percentage points. The authors flag high computational/memory cost as a limitation and propose future work with WiFi-6/7 APs and transformer-based architectures.</t>
+          <t>Buildings are rapidly becoming more digitized, to a large extent due to developments in IoT. This will provide many opportunities but also a number of challenges. One of the central challenges in the process of digitizing buildings is the ability to monitor the building's status effectively. Occupancy information, including people counting, occupancy detection, location tracking, and activity detection, plays a vital role in the management of smart buildings. In this article, our primary focus is on the use of Passive Infrared (PIR) sensors for gathering occupancy information. PIR sensors are among the most widely used sensors for this purpose due to their consideration of privacy concerns, cost-effectiveness, and low processing complexity compared to many others. This article provides a comprehensive literature review of PIR sensor technology from 2015 to 2023, with a focus on applications in people counting, activity detection, and localization. It consolidates findings from a number of articles that have explored and enhanced the capabilities of PIR sensors in these interconnected domains, examining various techniques, machine learning algorithms, and configurations, emphasizing not only data processing but also advantages, limitations, and efficacy in producing accurate occupancy information.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Dual GRU recurrent network with dynamic/static (DaS) feature preprocessing, subcarrier fusion, self-attention-based time-domain feature selection, and a spatial 'condition' branch (CNN) to distinguish LoS-blocking vs NLoS multipath cases; evaluated via real experiments in a two-room lab and a three-room conference-room testbed with commercial TP-Link routers (IEEE 802.11n), compared against R-TTWD and HARNN baselines.</t>
+          <t>Signal-based PIR sensors excel at localization/tracking while binary PIR sensors are better suited to activity detection across larger building areas; both types perform equally well for people counting. Deep learning approaches (DNNs, CNNs) are increasingly used to process signal-based PIR data for improved people-counting and localization accuracy, and strategic sensor placement/quantity matters more than raw sensor count - signal-based sensors can achieve higher accuracy with fewer units. The review maps PIR's evolving role in smart building energy efficiency, security and occupant comfort, and calls for further refinement of sensor tech and ML algorithms.</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Strong fit for SmartBuild's privacy-preserving, device-free occupancy/fall-context monitoring theme - shows camera-free, wearable-free multi-room presence detection is achievable with just one AP per room, directly supporting an argument for combining or contrasting WiFi CSI sensing with your BLE wearable design for elderly residents who may forget to wear a device.</t>
+          <t>Systematic literature review (2015-2023) of PIR-sensor occupancy-information research, categorising studies by sensor type (binary vs. signal-based), application (people counting, activity detection, localisation) and the machine learning/deep learning techniques (DNN, CNN, clustering) applied to PIR data.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Core occupancy-monitoring capability for the household system - PIR-based sensing is a low-cost, privacy-preserving option applicable to general household occupancy tracking, with elderly-resident monitoring as one specific application among several (security, energy management, general presence detection).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="160" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>PIR_Sensor-Based_Occupancy_Monitoring_in_Smart_Bui.pdf</t>
+          <t>2412.09980v1.pdf</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -2020,44 +2070,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>PIR Sensor-Based Occupancy Monitoring in Smart Buildings: A Review of Methodologies and Machine Learning Approaches</t>
+          <t>Real-Time Fall Detection Using Smartphone Accelerometers and WiFi Channel State Information</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Azad Shokrollahi; Jan Persson; Reza Malekian; Arezoo Sarkheyli-Hägele; Fredrik Karlsson</t>
+          <t>Lingyun Wang; Deqi Su; Aohua Zhang; Yujun Zhu; Weiwei Jiang; Xin He; Panlong Yang</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>Preprints.org, posted 29 Jan 2024, doi:10.20944/preprints202401.1924.v1 (not peer-reviewed preprint). Malmö University (Sweden) + Sony Network Communications.</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Buildings are rapidly becoming more digitized, to a large extent due to developments in IoT. This will provide many opportunities but also a number of challenges. One of the central challenges in the process of digitizing buildings is the ability to monitor the building's status effectively. Occupancy information, including people counting, occupancy detection, location tracking, and activity detection, plays a vital role in the management of smart buildings. In this article, our primary focus is on the use of Passive Infrared (PIR) sensors for gathering occupancy information. PIR sensors are among the most widely used sensors for this purpose due to their consideration of privacy concerns, cost-effectiveness, and low processing complexity compared to many others. This article provides a comprehensive literature review of PIR sensor technology from 2015 to 2023, with a focus on applications in people counting, activity detection, and localization. It consolidates findings from a number of articles that have explored and enhanced the capabilities of PIR sensors in these interconnected domains, examining various techniques, machine learning algorithms, and configurations, emphasizing not only data processing but also advantages, limitations, and efficacy in producing accurate occupancy information.</t>
-        </is>
+          <t>arXiv:2412.09980v1 [cs.LG], 13 Dec 2024. Submitted to IEEE Sensors Journal.</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>Signal-based PIR sensors excel at localization/tracking while binary PIR sensors are better suited to activity detection across larger building areas; both types perform equally well for people counting. Deep learning approaches (DNNs, CNNs) are increasingly used to process signal-based PIR data for improved people-counting and localization accuracy, and strategic sensor placement/quantity matters more than raw sensor count - signal-based sensors can achieve higher accuracy with fewer units. The review maps PIR's evolving role in smart building energy efficiency, security and occupant comfort, and calls for further refinement of sensor tech and ML algorithms.</t>
+          <t>In recent years, as the population ages, falls have increasingly posed a significant threat to the health of the elderly. We propose a real-time fall detection system that integrates the inertial measurement unit (IMU) of a smartphone with optimized WiFi channel state information (CSI) for secondary validation. Initially, the IMU distinguishes falls from routine daily activities with minimal computational demand. Subsequently, the CSI is employed for further assessment, which includes evaluating the individual's post-fall mobility. This methodology not only achieves high accuracy but also reduces energy consumption on the smartphone platform. An Android application developed specifically for this purpose issues an emergency alert if the user experiences a fall and is unable to move. Experimental results indicate that the CSI model, based on convolutional neural networks (CNN), achieves a detection accuracy of 99%, surpassing comparable IMU-only models, and demonstrating significant resilience in reducing false alarms.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Systematic literature review (2015-2023) of PIR-sensor occupancy-information research, categorising studies by sensor type (binary vs. signal-based), application (people counting, activity detection, localisation) and the machine learning/deep learning techniques (DNN, CNN, clustering) applied to PIR data.</t>
+          <t>The two-stage IMU-then-CSI pipeline achieves 99% fall-detection accuracy with the CSI-CNN stage, substantially reducing false positives compared to IMU-only systems, while keeping smartphone energy use low since CSI processing only triggers after a candidate fall event. The authors acknowledge the system's dependence on the phone being carried in a fixed pocket position as a key limitation, and propose future sensor fusion with wearable/ambient sensors to reduce this dependency and build a more robust hybrid fall-detection system.</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Directly relevant to SmartBuild's low-cost, privacy-preserving occupancy monitoring strand - PIR is a strong low-cost complement/alternative to your BLE-based occupancy detection, and this review's findings on sensor placement and ML processing choices are reusable evidence when justifying your own sensor/algorithm selections for elderly-resident room monitoring.</t>
+          <t>Two-stage cascade: an on-device IMU classifier flags candidate falls with minimal compute, then WiFi CSI (via CNN) performs secondary validation including post-fall mobility assessment (i.e., whether the person can still move) to reduce false alarms; deployed as an Android app that issues an automatic emergency alert when a fall plus immobility is detected.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-focused fall-detection use case within the household system's health-monitoring module - the two-stage 'cheap sensor screens, second modality confirms' design pattern is reusable more broadly for the system's general anomaly-detection logic across security and health functions.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="160" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>2412.09980v1.pdf</t>
+          <t>Journal of Computer Networks and Communications - 2024 - Hasan - Wearable Technology for Elderly Care  Integrating Health.pdf</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -2067,138 +2120,147 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Real-Time Fall Detection Using Smartphone Accelerometers and WiFi Channel State Information</t>
+          <t>Wearable Technology for Elderly Care: Integrating Health Monitoring and Emergency Alerts</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Lingyun Wang; Deqi Su; Aohua Zhang; Yujun Zhu; Weiwei Jiang; Xin He; Panlong Yang</t>
+          <t>Nowshad Hasan; Mohammad Faisal Ahmed</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2412.09980v1 [cs.LG], 13 Dec 2024. Submitted to IEEE Sensors Journal.</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>In recent years, as the population ages, falls have increasingly posed a significant threat to the health of the elderly. We propose a real-time fall detection system that integrates the inertial measurement unit (IMU) of a smartphone with optimized WiFi channel state information (CSI) for secondary validation. Initially, the IMU distinguishes falls from routine daily activities with minimal computational demand. Subsequently, the CSI is employed for further assessment, which includes evaluating the individual's post-fall mobility. This methodology not only achieves high accuracy but also reduces energy consumption on the smartphone platform. An Android application developed specifically for this purpose issues an emergency alert if the user experiences a fall and is unable to move. Experimental results indicate that the CSI model, based on convolutional neural networks (CNN), achieves a detection accuracy of 99%, surpassing comparable IMU-only models, and demonstrating significant resilience in reducing false alarms.</t>
-        </is>
+          <t>Wiley Journal of Computer Networks and Communications, vol. 2024, Article ID 5593708, 16 pages. doi:10.1155/jcnc/5593708. Chittagong University of Engineering &amp; Technology + International Islamic University Chittagong, Bangladesh.</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>2024</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>The two-stage IMU-then-CSI pipeline achieves 99% fall-detection accuracy with the CSI-CNN stage, substantially reducing false positives compared to IMU-only systems, while keeping smartphone energy use low since CSI processing only triggers after a candidate fall event. The authors acknowledge the system's dependence on the phone being carried in a fixed pocket position as a key limitation, and propose future sensor fusion with wearable/ambient sensors to reduce this dependency and build a more robust hybrid fall-detection system.</t>
+          <t>With the growing elderly population, ensuring consistent and reliable healthcare monitoring has become increasingly important. This research introduces an innovative solution in the form of a smart glove designed specifically for elderly care. The glove is equipped with advanced features such as fall detection, emergency messaging via hand gestures, and vital signs monitoring, including oxygen saturation (SpO2) and heart rate. The smart glove integrates the MPU6050 and MAX30100 sensors with Arduino and ESP8266 modules to achieve these functionalities. Fall detection is accurately identified by the MPU6050 sensor, while the MAX30100 sensor monitors SpO2 and heart rate. Hand gestures are recognized and interpreted for sending emergency messages. Data from these sensors are transmitted through IFTTT, enabling alerts and notifications via SMS, email, and a secured website, thus facilitating real-time remote monitoring and communication.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Two-stage cascade: an on-device IMU classifier flags candidate falls with minimal compute, then WiFi CSI (via CNN) performs secondary validation including post-fall mobility assessment (i.e., whether the person can still move) to reduce false alarms; deployed as an Android app that issues an automatic emergency alert when a fall plus immobility is detected.</t>
+          <t>The smart glove combining fall detection, gesture-based emergency messaging and SpO2/heart-rate monitoring in one wearable device demonstrated accurate, reliable readings across five senior test participants and represents a more comprehensive single-device solution than prior work that typically addresses only one function (e.g., only fall detection or only vitals). The authors flag further field evaluation in diverse real-world environments and integration of additional sensors/algorithms as future work.</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Strong match to SmartBuild's fall-detection and emergency-response goals - the two-stage 'cheap sensor screens, second modality confirms + assesses post-fall capacity to act' design pattern is directly reusable for justifying a layered BLE+secondary-sensor approach, and the 99% CSI-CNN accuracy figure is a useful benchmark citation.</t>
+          <t>IoT smart-glove prototype: MPU6050 accelerometer/gyroscope for fall detection and hand-gesture recognition, MAX30100 pulse oximeter for SpO2/heart-rate, Arduino + ESP8266 for processing/WiFi connectivity, IFTTT-based cloud pipeline pushing SMS/email/website alerts; validated with five senior participants comparing device readings against ground truth with MAE/error-percentage analysis.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care use-case precedent - a low-cost multi-function wearable (fall detection, vitals, emergency gesture) demonstrates how a single device can serve the household system's elderly-care module, while the gesture-based emergency channel is a reusable idea for the system's general emergency-alert design.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="160" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>sensors-25-02205.pdf</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+          <t>sensors-23-07927-2.pdf</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>A Decade of Progress in Wearable Sensors for Fall Detection (2015-2024): A Network-Based Visualization Review</t>
+          <t>Intelligent ADL Recognition via IoT-Based Multimodal Deep Learning Framework</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Yifei Li; Pei Liu; Yan Fang; Xiangyuan Wu; Yewei Xie; Zhongzhi Xu; Hao Ren; Fengshi Jing</t>
+          <t>Madiha Javeed; Naif Al Mudawi; Abdulwahab Alazeb; Sultan Almakdi; Saud S. Alotaibi; Samia Allaoua Chelloug; Ahmad Jalal</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Sensors, vol. 25, no. 7, article 2205, 2025. Hikvision Research Institute + Zhejiang University + City University of Macau + Duke-NUS + Sun Yat-sen University + Jinan University + UNC Chapel Hill.</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>Over the past decade, wearable sensors for fall detection have gained significant attention due to their potential in improving the safety of elderly users and reducing fall-related injuries. This review employs a network-based visualization approach to analyze research trends, key technologies, and collaborative networks. Using studies from SCI- and SSCI-indexed journals from 2015 to 2024, we analyzed 582 articles and 65 reviews with CiteSpace, revealing a significant rise in research on wearable sensors for fall detection. Additionally, we reviewed various datasets and machine learning techniques, from traditional methods to advanced deep learning frameworks, which demonstrate high accuracies, F1 scores, sensitivities, and specificities in controlled testing.</t>
-        </is>
+          <t>Sensors, vol. 23, no. 18, article 7927, 2023. doi 10.3390/s23187927. Received 25 Jul 2023, accepted 13 Sep 2023, published 16 Sep 2023. Air University Islamabad + Najran University + Umm Al-Qura University + Princess Nourah bint Abdulrahman University. Open access (CC BY 4.0).</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>2023</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>Wearable-sensor fall-detection research has grown steadily and diversified from simple accelerometer thresholding to deep learning frameworks with high reported accuracy in lab conditions. The authors note this is one of the first systematic bibliometric surveys of review papers (rather than primary studies) in this space, and call out cost, comfort, privacy and real-world (vs. lab) predictive reliability as the persistent open challenges that must be addressed for wearable fall-detection sensors to fulfil their potential in elderly care.</t>
+          <t>Smart home monitoring systems via internet of things (IoT) are required for taking care of elders at home. They provide the flexibility of monitoring elders remotely for their families and caregivers. Activities of daily living are an efficient way to effectively monitor elderly people at home and patients at caregiving facilities. The monitoring of such actions depends largely on IoT-based devices, either wireless or installed at different places. This paper proposes an effective and robust layered architecture using multisensory devices to recognize the activities of daily living from anywhere. Multimodality refers to the sensory devices of multiple types working together to achieve the objective of remote monitoring. Therefore, the proposed multimodal-based approach includes IoT devices, such as wearable inertial sensors and videos recorded during daily routines, fused together. The data from these multi-sensors have to be processed through a pre-processing layer through different stages, such as data filtration, segmentation, landmark detection, and 2D stick model. In the next layer, called the features processing, we have extracted, fused, and optimized different features from multimodal sensors. The final layer, called classification, has been utilized to recognize the activities of daily living via a deep learning technique known as convolutional neural network. It is observed from the proposed IoT-based multimodal layered system's results that an acceptable mean accuracy rate of 84.14% has been achieved.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Bibliometric/network-based visualization review using CiteSpace over 582 articles and 65 review papers (SCI/SSCI-indexed, 2015-2024), mapping research trends, key technologies, datasets and ML techniques (traditional to deep learning) and collaboration networks in wearable fall-detection research.</t>
+          <t>Our proposed method for IoT-based ADL recognition is an important novel idea for the elderly home monitoring system. It is a combination of multimodal-based sensors to compute the ADL recognition efficiently. Mean accuracies of 84.12% and 84.17% have been achieved over Opportunity++ and Berkeley-MHAD datasets. The results have shown that the proposed ADL recognition technique has outperformed other state-of-the-art methodologies. In the future the authors will focus on privacy issues and improving the 2D stick model, and note the system currently removes background from videos captured by immobile indoor cameras, so it may not generalise to different background settings.</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Useful high-level evidence base for SmartBuild's literature-review section on wearable fall detection - gives citable trend data (research volume growth, common ML techniques, persistent cost/comfort/privacy challenges) to frame why your own multi-sensor, BLE-based approach addresses gaps this review identifies.</t>
+          <t>Layered IoT architecture (pre-processing -&gt; feature processing -&gt; classification) fusing wearable inertial sensor data and video; CNN-based classification; experimental evaluation reaching 84.14% mean accuracy.</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Supports the household system's general multi-device sensor-fusion architecture (Section on Heterogeneity/Distributed Intelligence) - elderly ADL recognition is one use case demonstrating the layered wearable+video fusion approach, which the report can generalise to other household monitoring functions.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="160" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>healthcare-13-02066.pdf</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
+          <t>2311.09248v1-2.pdf</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>HAVE</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Wearable Devices &amp; Elderly: A Bibliometric Analysis of 2014-2024</t>
+          <t>Smart Home Goal Feature Model - A guide to support Smart Homes for Ageing in Place</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Haojun Zhi; Mariia Zolotova</t>
+          <t>Irini Logothetis; Priya Rani; Shangeetha Sivasothy; Rajesh Vasa; Kon Mouzakis</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Healthcare, vol. 13, no. 16, article 2066, 2025. doi:10.3390/healthcare13162066. Xi'an Jiaotong-Liverpool University + University of Liverpool.</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Background: The ageing population demands effective health solutions for the elderly. Wearable devices offer real-time monitoring and early alerts, but a comprehensive review of research in this field is lacking. This study uses bibliometric methods to analyse trends and advances in wearable devices for the elderly. Methods: Literature from 2014 to 2024 was retrieved from the Web of Science Core Collection using keywords related to the elderly and wearable devices. A total of 1015 English-language papers were analysed using tools including CiteSpace, VOSviewer, and R-Bibliometrix. Results: The annual growth rate of publications was 7.65%, with research increasing from 4 in 2014 to 1015 in 2024. Major contributors were the United States and China. Research shifted from fall detection and activity monitoring to heart rate variability, balance, and AI integration. Conclusions: Research on wearable devices for the elderly is growing rapidly. Future studies should focus on multimodal sensor fusion, AI-enhanced analytics and personalised health interventions, and long-term, real-world validation of wearable solutions to improve elderly health management.</t>
-        </is>
+          <t>arXiv:2311.09248v1, 2023. Applied Artificial Intelligence Institute, Deakin University + School of Engineering, RMIT University.</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>2023</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>The field has matured from foundational fall-detection/activity-monitoring work into sophisticated, AI-integrated systems, but two systemic barriers dominate: technology-adoption factors (usability, affordability, trust, self-efficacy) and infrastructural gaps - especially lack of interoperability between devices/healthcare systems and persistent data privacy/security concerns. The authors recommend future work prioritise multimodal sensor fusion, AI-enhanced analytics, personalised interventions and long-term real-world (not just lab) validation.</t>
+          <t>Smart technologies are significant in supporting ageing in place for elderly. Leveraging Artificial Intelligence (AI) and Machine Learning (ML), it provides peace of mind, enabling the elderly to continue living independently. Elderly use smart technologies for entertainment and social interactions, this can be extended to provide safety and monitor health and environmental conditions, detect emergencies and notify informal and formal caregivers when care is needed. This paper provides an overview of the smart home technologies commercially available to support ageing in place, the advantages and challenges of smart home technologies, and their usability from elderly's perspective. Synthesizing prior knowledge, we created a structured Smart Home Goal Feature Model (SHGFM) to resolve heuristic approaches used by the Subject Matter Experts (SMEs) at aged care facilities and healthcare researchers in adapting smart homes. The SHGFM provides SMEs the ability to (i) establish goals and (ii) identify features to set up strategies to design, develop and deploy smart homes for the elderly based on personalised needs. Our model provides guidance to healthcare researchers and aged care industries to set up smart homes based on the needs of elderly, by defining a set of goals at different levels mapped to a different set of features.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Bibliometric analysis of 1015 English-language Web of Science papers (2014-2024) using CiteSpace, VOSviewer and R-Bibliometrix to map publication growth, leading contributors/authors (Bijan Najafi, Lynn Rochester), and thematic evolution (fall detection -&gt; heart rate variability, balance, AI integration).</t>
+          <t>This paper synthesises the knowledge in smart home technologies supporting ageing in place into a structured Smart Home Goal Feature Model (SHGFM), providing a tool SMEs can use to identify the level of smart home support an elderly person needs based on case-by-case assessment. Previous research indicates current holistic approaches to smart home systems for the elderly result in low adoption, often due to poor interface design, privacy and trust issues, and economic or educational barriers. The SHGFM resolves this by defining a set of goals at different levels mapped to a corresponding set of features, guiding healthcare researchers and aged care industries in designing, developing and deploying smart homes based on personalised elderly needs.</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Complements the fall-detection bibliometric review above with a broader lens on elderly wearables generally - its identification of interoperability and privacy/trust as the top non-technical adoption barriers is directly citable for SmartBuild's discussion of why BLE interoperability and privacy-by-design matter for elderly user acceptance.</t>
+          <t>Literature synthesis + design of a structured Smart Home Goal Feature Model (SHGFM) mapping elderly-care goals to smart home features.</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-specific framework, but its goal-to-feature mapping methodology is reusable for the household system's Recommendations section more broadly - supports the report's device/protocol-justification approach (why BLE, why particular sensors) for whichever household need is being addressed, not only ageing-in-place.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="160" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Journal of Computer Networks and Communications - 2024 - Hasan - Wearable Technology for Elderly Care  Integrating Health.pdf</t>
+          <t>2304.13107v2.pdf</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -2208,44 +2270,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Wearable Technology for Elderly Care: Integrating Health Monitoring and Emergency Alerts</t>
+          <t>Time-Selective RNN for Device-Free Multi-Room Human Presence Detection Using WiFi CSI</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Nowshad Hasan; Mohammad Faisal Ahmed</t>
+          <t>Li-Hsiang Shen; An-Hung Hsiao; Fang-Yu Chu; Kai-Ten Feng</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Wiley Journal of Computer Networks and Communications, vol. 2024, Article ID 5593708, 16 pages. doi:10.1155/jcnc/5593708. Chittagong University of Engineering &amp; Technology + International Islamic University Chittagong, Bangladesh.</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>With the growing elderly population, ensuring consistent and reliable healthcare monitoring has become increasingly important. This research introduces an innovative solution in the form of a smart glove designed specifically for elderly care. The glove is equipped with advanced features such as fall detection, emergency messaging via hand gestures, and vital signs monitoring, including oxygen saturation (SpO2) and heart rate. The smart glove integrates the MPU6050 and MAX30100 sensors with Arduino and ESP8266 modules to achieve these functionalities. Fall detection is accurately identified by the MPU6050 sensor, while the MAX30100 sensor monitors SpO2 and heart rate. Hand gestures are recognized and interpreted for sending emergency messages. Data from these sensors are transmitted through IFTTT, enabling alerts and notifications via SMS, email, and a secured website, thus facilitating real-time remote monitoring and communication.</t>
-        </is>
+          <t>arXiv:2304.13107v2 [cs.AI], 2023. National Central University + National Yang Ming Chiao Tung University (NYCU), Taiwan.</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>2023</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>The smart glove combining fall detection, gesture-based emergency messaging and SpO2/heart-rate monitoring in one wearable device demonstrated accurate, reliable readings across five senior test participants and represents a more comprehensive single-device solution than prior work that typically addresses only one function (e.g., only fall detection or only vitals). The authors flag further field evaluation in diverse real-world environments and integration of additional sensors/algorithms as future work.</t>
+          <t>Device-free human presence detection is a crucial technology for various applications, including home automation, security, and healthcare. While camera-based systems have traditionally been used for this purpose, they raise privacy concerns. To address this issue, recent research has explored the use of wireless channel state information (CSI) extracted from commercial WiFi access points (APs). In this paper, we propose a device-free human presence detection system for multi-room scenarios using a time-selective conditional dual feature extract recurrent network (TCD-FERN). Our system captures significant time features using a dynamic and static data preprocessing technique, extracting both moving and spatial features and differentiating between line-of-sight (LoS) and non-line-of-sight (NLoS) cases. A voting scheme is adopted to mitigate the feature attenuation problem caused by room partitions, with around 3% improvement of human presence detection accuracy. Compared to existing works, our proposed TCD-FERN system can achieve above 97% of human presence detection accuracy for multi-room scenarios with the adoption of fewer WiFi APs.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>IoT smart-glove prototype: MPU6050 accelerometer/gyroscope for fall detection and hand-gesture recognition, MAX30100 pulse oximeter for SpO2/heart-rate, Arduino + ESP8266 for processing/WiFi connectivity, IFTTT-based cloud pipeline pushing SMS/email/website alerts; validated with five senior participants comparing device readings against ground truth with MAE/error-percentage analysis.</t>
+          <t>TCD-FERN achieves over 97% multi-room presence detection accuracy using only one WiFi AP per room (a star topology transmitter-in-centre design), substantially outperforming existing benchmarks (R-TTWD, HARNN) by roughly 20-40%. Detection is notably harder for the transmitter's own room due to signal attenuation through walls, which the proposed voting scheme improves by up to ~12 percentage points. The authors flag high computational/memory cost as a limitation and propose future work with WiFi-6/7 APs and transformer-based architectures.</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Strong precedent for SmartBuild's wearable component - demonstrates a low-cost (Arduino/ESP8266) multi-function elderly wearable combining fall detection, vitals and an intentional emergency-gesture channel, useful when justifying combining several sensing functions into a single low-cost wearable rather than separate devices.</t>
+          <t>Dual GRU recurrent network with dynamic/static (DaS) feature preprocessing, subcarrier fusion, self-attention-based time-domain feature selection, and a spatial 'condition' branch (CNN) to distinguish LoS-blocking vs NLoS multipath cases; evaluated via real experiments in a two-room lab and a three-room conference-room testbed with commercial TP-Link routers (IEEE 802.11n), compared against R-TTWD and HARNN baselines.</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>Core household-wide, privacy-preserving presence-detection capability - camera-free, wearable-free multi-room detection using WiFi CSI is general-purpose and supports the report's core occupancy/security-monitoring design; elderly residents who may forget to wear a device are one beneficiary group among the household generally.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="160" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>igaa057.1318.pdf</t>
+          <t>ijmr_v11i2e39005.pdf</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -2255,44 +2320,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>GSA 2020 Annual Scientific Meeting Abstracts (Innovation in Aging, Vol 4, Suppl 1) - including 'In-Home Resourcefulness' / Grandfamilies Support-Group Study and 'A Systematic Review of In-Home Smart Technology Adoption to Improve Older Adult Health and Family Caregiving'</t>
+          <t>In-Home Monitoring Technology for Aging in Place: Scoping Review</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Multiple authors incl. (support-group/resourcefulness study authors); Geunhye Park; Erin Robinson (systematic review abstract), University of Missouri-Columbia; plus Hyun-E Yeom, Misook Jung, Eunyoung Park (Chungnam National University); Nadia Firdausya, Alex Bishop, Barbara Carlson, Weihua Sheng (Oklahoma State University)</t>
+          <t>Daejin Kim; Hongyi Bian; Carl K Chang; Liang Dong; Jennifer Margrett</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Innovation in Aging, 2020, vol. 4, supplement 1, p. 409, Gerontological Society of America (GSA) 2020 Annual Scientific Meeting conference abstracts (poster session 'Technology II').</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>This page compiles several conference abstracts. Most relevant is a study on grandparent caregivers ('grandfamilies') and support-group participation: of the sample, 53.8% (N=184) belonged to a support group (mostly online/Facebook), and knowing other families like their own affected self-appraised stress; grandmothers in support groups reported lower mindfulness, higher stress and worse mental health scores than non-participants, likely reflecting greater underlying need for support. An adjacent abstract, 'A Systematic Review of In-Home Smart Technology Adoption to Improve Older Adult Health and Family Caregiving' (Park &amp; Robinson), reviewed 1,227 identified articles (1991-2019) down to 48 included studies and found key facilitators of smart-technology adoption (technology familiarity, safety/security, personalised/non-obtrusive design, easy access, reduced caregiver burden) and barriers (cost, difficulty of use, time, stigma, privacy, data accuracy, confidence).</t>
-        </is>
+          <t>Interactive Journal of Medical Research (iJMR), 2022, article e39005. Iowa State University.</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>2022</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Both abstracts are systematic-review/survey findings rather than novel systems: the grandfamilies study highlights that caregiver support-group participation correlates with (but does not straightforwardly reduce) stress, suggesting unmet support needs among caregivers of higher burden; the smart-technology adoption review concludes that addressing the identified facilitators/barriers (especially non-obtrusive design, privacy and cost) is crucial for successful dissemination of in-home smart technologies among older adults and family caregivers.</t>
+          <t>Background: For successful aging-in-place strategy development, in-home monitoring technology is necessary as a new home modification strategy. Monitoring an older adult's daily physical activity at home can positively impact their health and well-being by providing valuable information about functional, cognitive, and social health status. However, it is questionable how these in-home monitoring technologies have changed the traditional residential environment. Objective: The main purpose of this study was to classify recent smart home technologies that monitor older adults' health and to architecturally describe these technologies as they are used in older adults' homes. Methods: The scoping review method was employed to identify key characteristics of in-home monitoring technologies for older adults. In June 2021, four databases, including Web of Science, IEEE Xplore, ACM Digital Library, and Scopus, were searched for peer-reviewed articles.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Conference abstracts: (a) cross-sectional survey analysis of grandparent caregivers' support-group participation vs. mindfulness/stress/mental-health outcomes; (b) systematic literature review (Rew method, 1991-2019, Web of Science/PubMed/Scopus/CINAHL/PsycInfo, 1,227 -&gt; 48 articles) of facilitators/barriers to in-home internet-based smart technology adoption by older adults and family caregivers.</t>
+          <t>In-home monitoring technologies play an essential role in aging in place by tracking older adults' daily activities and identifying health-related issues, enabling proactive rather than reactive care and early intervention. The review highlights that these technologies are typically retrofitted into existing homes rather than designed in from the start, and stresses the importance of appropriate strategies for smart home design (including telehealth/online communication) to address societal issues like overcrowding, driving limitations and infection risk. Limitations include restricting the search to June 2016-2021, English-only articles, and single-reviewer study selection (though findings were discussed among all authors).</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Explicitly retained per your instruction - grounds SmartBuild's human-factors/adoption discussion for family caregivers of the elderly (not just the older adult end-user), and the facilitators/barriers list (non-obtrusive design, privacy, cost, stigma) is directly citable evidence for your design-rationale section on why SmartBuild aims for an unobtrusive, low-stigma, privacy-respecting BLE wearable rather than a more visible/invasive alternative.</t>
+          <t>Scoping review of peer-reviewed articles (June 2016-2021) across Web of Science, IEEE Xplore, ACM Digital Library and Scopus, classifying in-home monitoring technologies for older adults and architecturally describing how they are deployed/integrated within the home environment; includes appendices summarising 30 included studies.</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Elderly/ageing-in-place use case, but its classification scheme for in-home monitoring technologies is reusable background for the household system's overall approach to retrofitting sensing infrastructure into existing housing stock, relevant beyond the elderly-care module alone.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="160" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ijmr_v11i2e39005.pdf</t>
+          <t>2204.05921v2.pdf</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -2302,44 +2370,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>In-Home Monitoring Technology for Aging in Place: Scoping Review</t>
+          <t>Internet of Things Device Capabilities, Architectures, Protocols, and Smart Applications in Healthcare Domain: A Review</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Daejin Kim; Hongyi Bian; Carl K Chang; Liang Dong; Jennifer Margrett</t>
+          <t>Md. Milon Islam; Sheikh Nooruddin; Fakhri Karray; Ghulam Muhammad</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Interactive Journal of Medical Research (iJMR), 2022, article e39005. Iowa State University.</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Background: For successful aging-in-place strategy development, in-home monitoring technology is necessary as a new home modification strategy. Monitoring an older adult's daily physical activity at home can positively impact their health and well-being by providing valuable information about functional, cognitive, and social health status. However, it is questionable how these in-home monitoring technologies have changed the traditional residential environment. Objective: The main purpose of this study was to classify recent smart home technologies that monitor older adults' health and to architecturally describe these technologies as they are used in older adults' homes. Methods: The scoping review method was employed to identify key characteristics of in-home monitoring technologies for older adults. In June 2021, four databases, including Web of Science, IEEE Xplore, ACM Digital Library, and Scopus, were searched for peer-reviewed articles.</t>
-        </is>
+          <t>IEEE Sensors Journal (preprint, arXiv:2204.05921v2), University of Waterloo + King Saud University.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>2022</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>In-home monitoring technologies play an essential role in aging in place by tracking older adults' daily activities and identifying health-related issues, enabling proactive rather than reactive care and early intervention. The review highlights that these technologies are typically retrofitted into existing homes rather than designed in from the start, and stresses the importance of appropriate strategies for smart home design (including telehealth/online communication) to address societal issues like overcrowding, driving limitations and infection risk. Limitations include restricting the search to June 2016-2021, English-only articles, and single-reviewer study selection (though findings were discussed among all authors).</t>
+          <t>Nowadays, the Internet has spread to practically every country around the world and is having unprecedented effects on people's lives. The Internet of Things (IoT) is getting more popular and has a high level of interest in both practitioners and academicians in the age of wireless communication due to its diverse applications. In this paper, the most common and popular IoT device capabilities, architectures, and protocols are demonstrated in brief to provide a clear overview of the IoT technology to researchers. The common IoT device capabilities including hardware (Raspberry Pi, Arduino, and ESP8266) and software (operating systems, and built-in tools) platforms are described in detail. The widely used architectures include the three-layer architecture, SOA-based architecture, and middleware-based architecture. The popular protocols for IoT are demonstrated including CoAP, MQTT, XMPP, AMQP, DDS, 6LoWPAN, BLE, and Zigbee. Additionally, this research provides an in-depth overview of potential healthcare applications based on IoT technologies, summarizing state-of-the-art knowledge, open issues and shortcomings, and recommendations for further studies.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Scoping review of peer-reviewed articles (June 2016-2021) across Web of Science, IEEE Xplore, ACM Digital Library and Scopus, classifying in-home monitoring technologies for older adults and architecturally describing how they are deployed/integrated within the home environment; includes appendices summarising 30 included studies.</t>
+          <t>The paper synthesises IoT hardware, architecture and protocol choices specifically for healthcare deployment and identifies four major open-challenge categories with recommendations: security/privacy (encryption, blockchain, AI-based anomaly detection), standardization/interoperability (standard service-description languages, open-source implementations), data variability/scalability (big-data warehousing, lightweight SOA), and power/cost efficiency (solar-powered hardware, multi-purpose devices). The authors conclude these must be resolved together for large-scale IoT healthcare networks to succeed.</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Directly relevant background for SmartBuild's aging-in-place framing - provides a classification scheme for in-home monitoring technologies and reinforces the retrofit-vs-designed-in distinction relevant to deploying your system in existing Kāinga Ora housing stock rather than new-build homes.</t>
+          <t>Structured literature synthesis covering IoT device hardware capabilities (Raspberry Pi, Arduino, ESP8266), architectural patterns (three-layer, SOA-based, middleware-based) and communication protocols (CoAP, MQTT, XMPP, AMQP, DDS, 6LoWPAN, BLE, Zigbee), cross-referenced against healthcare application domains and a structured table of deployment challenges/recommendations.</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>General IoT architecture/protocol reference for the household system's technical design (healthcare framing, but hardware/protocol choices apply system-wide) - its security/interoperability/scalability/power challenge-recommendation table is directly reusable for documenting the whole system's architecture choices and limitations, not only the elderly-care component.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="160" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>2204.05921v2.pdf</t>
+          <t>2208.10659v1.pdf</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -2349,44 +2420,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Internet of Things Device Capabilities, Architectures, Protocols, and Smart Applications in Healthcare Domain: A Review</t>
+          <t>Fall Detection from Audios with Audio Transformers</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Md. Milon Islam; Sheikh Nooruddin; Fakhri Karray; Ghulam Muhammad</t>
+          <t>Prabhjot Kaur; Qifan Wang; Weisong Shi</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>IEEE Sensors Journal (preprint, arXiv:2204.05921v2), University of Waterloo + King Saud University.</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Nowadays, the Internet has spread to practically every country around the world and is having unprecedented effects on people's lives. The Internet of Things (IoT) is getting more popular and has a high level of interest in both practitioners and academicians in the age of wireless communication due to its diverse applications. In this paper, the most common and popular IoT device capabilities, architectures, and protocols are demonstrated in brief to provide a clear overview of the IoT technology to researchers. The common IoT device capabilities including hardware (Raspberry Pi, Arduino, and ESP8266) and software (operating systems, and built-in tools) platforms are described in detail. The widely used architectures include the three-layer architecture, SOA-based architecture, and middleware-based architecture. The popular protocols for IoT are demonstrated including CoAP, MQTT, XMPP, AMQP, DDS, 6LoWPAN, BLE, and Zigbee. Additionally, this research provides an in-depth overview of potential healthcare applications based on IoT technologies, summarizing state-of-the-art knowledge, open issues and shortcomings, and recommendations for further studies.</t>
-        </is>
+          <t>arXiv:2208.10659v1 [cs.SD], 2022. Wayne State University + Meta AI.</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>2022</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>The paper synthesises IoT hardware, architecture and protocol choices specifically for healthcare deployment and identifies four major open-challenge categories with recommendations: security/privacy (encryption, blockchain, AI-based anomaly detection), standardization/interoperability (standard service-description languages, open-source implementations), data variability/scalability (big-data warehousing, lightweight SOA), and power/cost efficiency (solar-powered hardware, multi-purpose devices). The authors conclude these must be resolved together for large-scale IoT healthcare networks to succeed.</t>
+          <t>Fall detection for the elderly is a well-researched problem with several proposed solutions, including wearable and non-wearable techniques. While the existing techniques have excellent detection rates, their adoption by the target population is lacking due to the need for wearing devices and user privacy concerns. Our paper investigates ambient sound input for fall detection among the elderly, especially targeting environments such as bathrooms where other sensing techniques (cameras, wearables) are often impractical or privacy-invasive. We develop and train a Transformer-based deep learning model to detect fall events from sound input, and additionally implement the solution on an autonomous mobile robot to provide broader sensing coverage.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Structured literature synthesis covering IoT device hardware capabilities (Raspberry Pi, Arduino, ESP8266), architectural patterns (three-layer, SOA-based, middleware-based) and communication protocols (CoAP, MQTT, XMPP, AMQP, DDS, 6LoWPAN, BLE, Zigbee), cross-referenced against healthcare application domains and a structured table of deployment challenges/recommendations.</t>
+          <t>The Transformer-based ambient-sound fall-detection model offers a non-wearable, non-intrusive and scalable solution particularly suited to privacy-sensitive spaces like bathrooms where cameras/wearables are impractical; deploying it on a mobile robot extends sensing coverage beyond fixed microphones. The authors plan to extend the solution to other indoor environments beyond the bathroom (with additional training) and to collect a greater variety of fall events and explore additional audio features to further improve results.</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Useful architecture/protocol reference for SmartBuild's technical design section - its comparison of hardware platforms (Arduino/ESP8266/Raspberry Pi, matching several other papers in your matrix) and its security/interoperability/scalability/power challenge-recommendation table are directly reusable when documenting your own architecture choices and known limitations.</t>
+          <t>Audio Spectrogram Transformer-style deep learning model trained on ambient sound recordings to classify fall vs. non-fall audio events; deployed both as a fixed sensor and on an autonomous mobile robot platform for extended room coverage.</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care use case (bathroom privacy) within the household system's health-monitoring module - ambient audio sensing is a reusable privacy-preserving technique the report can position as a general household sensing option for private spaces, with elderly fall-detection as the specific example given.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="160" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>challenges-and-issues-in-multisensor-fusion-approach-for-17vbnje5m3.pdf</t>
+          <t>Journal of Sensors - 2022 - De Raeve - Bluetooth%E2%80%90Low%E2%80%90Energy%E2%80%90Based Fall Detection and Warning System for Elderly People in.pdf</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -2396,44 +2470,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Challenges and Issues in Multisensor Fusion Approach for Fall Detection: Review Paper</t>
+          <t>Bluetooth-Low-Energy-Based Fall Detection and Warning System for Elderly People in Nursing Homes</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Gregory Koshmak; Amy Loutfi; Maria Linden</t>
+          <t>Nick De Raeve; Adnan Shahid; Matthias de Schepper; Eli De Poorter; Ingrid Moerman; Jo Verhaevert; Patrick Van Torre; Hendrik Rogier</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Hindawi Journal of Sensors, vol. 2016, Article ID 6931789, 12 pages. Mälardalen University + Örebro University, Sweden.</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>Emergency situations associated with falls are a serious concern for an aging society. Yet following recent development within ICT, a significant number of solutions have been proposed to track body movement and detect falls using various sensor technologies, thereby facilitating fall detection and in some cases prevention. A number of recent reviews on fall detection methods using ICT technologies have emerged in the literature and an increasingly popular approach considers combining information from several sensor sources to assess falls. The aim of this paper is to review in detail the subfield of fall detection techniques that explicitly considers the use of multisensor fusion based methods to assess and determine falls. The paper highlights key differences between the single sensor-based approach and a multifusion one, describes and categorizes the various systems used, provides information on the challenges of a multifusion approach, and finally discusses trends for future work.</t>
-        </is>
+          <t>Hindawi Journal of Sensors, vol. 2022, Article ID 9930681, 14 pages. doi:10.1155/2022/9930681. IDLab, Ghent University-imec, Belgium.</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>2022</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Multisensor fusion inherits most single-sensor fall-detection challenges (poor real-world performance vs. lab conditions, limited usability especially for wearables/smartphones, privacy concerns) plus fusion-specific problems: lack of a simplified/standardised evaluation procedure, added computational cost from processing multiple data streams (mitigated by staged preprocessing/filtering/feature-extraction pipelines), and difficulty integrating sensors with distinct technological backgrounds. The authors recommend building test environments that combine wearable, ambient and vision sensors, adding sensor types only as needed per patient/use-case to avoid data overload and unnecessary privacy violations.</t>
+          <t>Due to the ever growing population of elderly people, there is a dramatic increase in fall accidents. Currently, multiple ideas exist to prevent the elderly from falling, by means of technology or individualised fall prevention training programs. Most of them are costly, difficult to implement or less used by the elderly, and they do not deliver the required results. Furthermore, the increasingly older population will also impact the workload of medical and nursing personnel. Therefore, we propose a novel fall detection and warning system for nursing homes, relying on Bluetooth Low Energy wireless communication. This paper describes the hardware design of a fall-acceleration sensing wearable for the elderly, a novel algorithm for real-time filtering of the measurement data, and a strategy to confirm detected fall events based on changes in the person's orientation. We also compare the algorithm's performance to a machine learning procedure using a convolutional neural network.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Structured literature review categorising multisensor fall-detection systems by sensor combination type (wearable+ambient, wearable+vision, etc.), summarising evaluation methodologies used across reviewed studies, and identifying and discussing recurring implementation and evaluation challenges.</t>
+          <t>The wearable's dual-confirmation approach (acceleration peak + orientation-change confirmation) makes a false confirmed fall alert virtually impossible, validated across three open-source databases (85 persons, 18,835 ADL/fall activities) achieving F1 scores of 82.94-89.8% for the rule-based algorithm, comparable to a CNN-based ML approach (86.72-95.09% F1). The unobtrusive wearable fits in a 32x23x10mm package, is energy-efficient via BLE and low-power accelerometer modes (e.g., during sleep), and provides excellent room coverage at low energy consumption - directly meeting the paper's design requirements for reliability and unobtrusiveness in a nursing-home deployment.</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Directly supports SmartBuild's sensor-fusion design rationale for fall detection - its finding that fusion systems should add sensor types only per actual patient need (to avoid data overload and privacy violations) is a strong citable justification for keeping your own multi-sensor design deliberately minimal/purposeful rather than maximalist.</t>
+          <t>BLE-based wearable with a three-axis accelerometer: fall-peak detection via acceleration threshold (2.5g) plus a second independent confirmation signal from spatial-orientation change (60 degree threshold), 5ms sampling rate; validated via a dedicated measurement campaign (including harmless high-acceleration events like sitting down) and against three open-source fall-detection datasets; rule-based algorithm benchmarked against a CNN machine-learning alternative.</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Strongest elderly-care use-case precedent in the matrix - a compact BLE wearable with dual-signal false-alarm rejection for nursing-home fall detection; useful primarily as a benchmark and architectural precedent for the household system's elderly-care module specifically, within the report's broader household-security framing.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="160" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>PID5934743.pdf</t>
+          <t>2101.06519v1.pdf</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -2443,44 +2520,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Comparison of Zigbee, Z-Wave, Wi-Fi, and Bluetooth Wireless Technologies Used in Home Automation</t>
+          <t>Intrusion Detection Systems for Smart Home IoT Devices: Experimental Comparison Study</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Salim Jibrin Danbatta; Asaf Varol</t>
+          <t>Faisal Alsakran; Gueltoum Bendiab; Stavros Shiaeles; Nicholas Kolokotronis</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Proceedings of the 2019 7th International Symposium on Digital Forensics and Security (ISDFS). Firat University, Turkey.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Most of the home automation wireless technologies on the internet of things are based on ZigBee, Z-Wave, Wi-Fi, and Bluetooth wireless technologies. While these solutions are good enough, users of smart homes are facing challenges of selecting the best technology. This paper compares the performance of ZigBee, Z-Wave, Wi-Fi and Bluetooth technologies from the user's perspective. Power consumption, range, cost, ease of use, scalability, and interoperability are the six indices developed as guidelines to potential users, and hence, the results of this study. With this knowledge, users can make the appropriate choice of wireless technology solution to use in their home automation systems.</t>
-        </is>
+          <t>arXiv:2101.06519v1, 2021. University of Plymouth (UK) + University of Portsmouth (UK) + University of Peloponnese (Greece).</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>2021</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>No single protocol wins on every index: Bluetooth is the lowest-cost and lowest-power option but has the shortest range (10m) and is best for simple, low-node-count control; ZigBee offers a good range (100m) and moderate scalability but weaker cross-vendor interoperability; Z-Wave (30m range) is judged best for scalability and interoperability across many devices from different manufacturers due to its certified compatibility standard; Wi-Fi offers the longest range (up to 1000m) but at higher cost and power draw. The authors conclude protocol choice should be driven by the specific home-automation use case's priorities among these six indices.</t>
+          <t>Smart homes are one of the most promising applications of the emerging Internet of Things (IoT) technology. With the growing number of IoT related devices such as smart thermostats, smart fridges, smart speakers, smart light bulbs and smart locks, smart homes promise to make our lives easier and more comfortable. However, the increased deployment of such smart devices brings an increase in potential security risks and home privacy breaches. In order to overcome such risks, Intrusion Detection Systems are presented as pertinent tools that can provide network-level protection for smart devices deployed in home environments. This paper experimentally compares three open-source IDS systems - Snort, Suricata and Bro - specifically in terms of resource consumption for smart home deployment scenarios.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Comparative literature-based analysis of ZigBee, Z-Wave, Wi-Fi and Bluetooth across six user-relevant indices (power consumption, range, cost, ease of use, scalability, interoperability), including a device/technology mapping table (e.g., iPhone/Bluetooth+WiFi, Fitbit/Bluetooth, Samsung Smart TV/WiFi+Z-Wave).</t>
+          <t>Suricata and Bro/Zeek consistently used less CPU and RAM than Snort 3 across the malware/attack traffic samples tested, making them more resource-appropriate for the constrained hardware typical of smart home gateways; Snort recorded the highest CPU utilisation (60-70%) versus 20-40% for the other two. The authors plan future work comparing detection accuracy (not just resource use) across larger packet-capture datasets and testing in a real smart-home environment rather than simulation via Docker containers.</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Reusable protocol-comparison evidence for SmartBuild's technology-selection rationale, similar in scope to the other wireless-standard-comparison papers in your matrix - its six-index framework (power/range/cost/ease-of-use/scalability/interoperability) gives you a ready-made structure for justifying BLE's fit versus ZigBee/Z-Wave/Wi-Fi for a single-resident elderly home deployment.</t>
+          <t>Experimental resource-consumption benchmarking of three open-source network Intrusion Detection Systems (Snort, Suricata, Bro/Zeek) deployed in Docker containers, measuring CPU and RAM utilisation against a set of malware/attack PCAP traffic samples representative of smart-home network threats.</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Core household-security evidence - network-level intrusion detection for the smart-home gateway/hub is general-purpose and applies to the whole household system's security backbone (protecting all data flows, not just elderly health data); gives concrete resource-usage benchmarks for choosing a lightweight IDS.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="160" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>2101.06519v1.pdf</t>
+          <t>IoT-BasedSmartSecuritySystemonaDoorLockApplication.pdf</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -2490,44 +2570,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Intrusion Detection Systems for Smart Home IoT Devices: Experimental Comparison Study</t>
+          <t>IoT-Based Smart Security System on a Door Lock Application</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Faisal Alsakran; Gueltoum Bendiab; Stavros Shiaeles; Nicholas Kolokotronis</t>
+          <t>Debabrata Dansana; Brojo Kishore Mishra; K. Sindhuja; Subhashree Sahoo</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2101.06519v1, 2021. University of Plymouth (UK) + University of Portsmouth (UK) + University of Peloponnese (Greece).</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Smart homes are one of the most promising applications of the emerging Internet of Things (IoT) technology. With the growing number of IoT related devices such as smart thermostats, smart fridges, smart speakers, smart light bulbs and smart locks, smart homes promise to make our lives easier and more comfortable. However, the increased deployment of such smart devices brings an increase in potential security risks and home privacy breaches. In order to overcome such risks, Intrusion Detection Systems are presented as pertinent tools that can provide network-level protection for smart devices deployed in home environments. This paper experimentally compares three open-source IDS systems - Snort, Suricata and Bro - specifically in terms of resource consumption for smart home deployment scenarios.</t>
-        </is>
+          <t>Book chapter/conference proceedings (Springer), India.</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>2021</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>Suricata and Bro/Zeek consistently used less CPU and RAM than Snort 3 across the malware/attack traffic samples tested, making them more resource-appropriate for the constrained hardware typical of smart home gateways; Snort recorded the highest CPU utilisation (60-70%) versus 20-40% for the other two. The authors plan future work comparing detection accuracy (not just resource use) across larger packet-capture datasets and testing in a real smart-home environment rather than simulation via Docker containers.</t>
+          <t>The Internet of Things (IoT) is the term that describes the communication between physical objects, also known as the 'things,' with the interconnection network. The keys to a smart home depend upon the security of the door. If the entrance of the home is secured, then the home will be more secure. Senior citizens and children are there at home, and their security should not be hampered at all when the owner is absent. From the concept of smart home, a smart door unlocking system has been proposed that uses infrared sensors and an Arduino board to give an alarm when any suspicious activity is going on. This paper revolves around IoT security which mainly focuses on home automation, designed to help an individual secure his/her house from theft; if someone breaks the door or enters the wrong password, it directly informs the concerned owner.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Experimental resource-consumption benchmarking of three open-source network Intrusion Detection Systems (Snort, Suricata, Bro/Zeek) deployed in Docker containers, measuring CPU and RAM utilisation against a set of malware/attack PCAP traffic samples representative of smart-home network threats.</t>
+          <t>The proposed mini-computer-based home security system achieves low cost and stable operation with the key advantage of being fully automated - once installed it requires no further human interaction. The authors note future work will target a sustainable/renewable power source and remote operability, plus capturing and sending photos of anyone who enters a wrong password to the homeowner.</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Supports SmartBuild's security/privacy discussion around the home gateway/hub - relevant if your report addresses network-level protection for the BLE-to-cloud bridge in the home, since it gives concrete resource-usage data for choosing a lightweight IDS suitable for constrained smart-home hardware rather than a heavier general-purpose one.</t>
+          <t>Arduino-based smart door lock combining infrared sensors for intrusion/suspicious-activity detection with password-based unlocking; hardware+software system where incorrect password entry or forced door opening triggers an alert to the homeowner.</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Core household-security use case - an automated door-lock/entry-security system explicitly designed to protect all occupants (elderly and otherwise) when the owner is absent; supports the report's central security-protocol section as a complementary safety layer alongside health/occupancy monitoring.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="160" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>IoT-BasedSmartSecuritySystemonaDoorLockApplication.pdf</t>
+          <t>2107.09509v1.pdf</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -2537,44 +2620,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>IoT-Based Smart Security System on a Door Lock Application</t>
+          <t>Wearable Health Monitoring System for Older Adults in a Smart Home Environment</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Debabrata Dansana; Brojo Kishore Mishra; K. Sindhuja; Subhashree Sahoo</t>
+          <t>Rajdeep Kumar Nath; Himanshu Thapliyal</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Book chapter/conference proceedings (Springer), India.</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>The Internet of Things (IoT) is the term that describes the communication between physical objects, also known as the 'things,' with the interconnection network. The keys to a smart home depend upon the security of the door. If the entrance of the home is secured, then the home will be more secure. Senior citizens and children are there at home, and their security should not be hampered at all when the owner is absent. From the concept of smart home, a smart door unlocking system has been proposed that uses infrared sensors and an Arduino board to give an alarm when any suspicious activity is going on. This paper revolves around IoT security which mainly focuses on home automation, designed to help an individual secure his/her house from theft; if someone breaks the door or enters the wrong password, it directly informs the concerned owner.</t>
-        </is>
+          <t>arXiv:2107.09509v1 [eess.SP], 2021. University of Kentucky.</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>2021</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>The proposed mini-computer-based home security system achieves low cost and stable operation with the key advantage of being fully automated - once installed it requires no further human interaction. The authors note future work will target a sustainable/renewable power source and remote operability, plus capturing and sending photos of anyone who enters a wrong password to the homeowner.</t>
+          <t>The advent of IoT has enabled the design of connected and integrated smart health monitoring systems. These smart health monitoring systems could be realized in a smart home context to render long-term care to the elderly population. In this paper, we present the design of a wearable health monitoring system suitable for older adults in a smart home context. The proposed system offers solutions to monitor the stress, blood pressure, and location of an individual within a smart home environment. The stress detection model uses electrodermal activity (EDA), photoplethysmography (PPG) and skin temperature (ST) signals from a smart wristband, transmitted via low-energy Bluetooth to a companion app and then to the smart-home cloud via WiFi; a separate framework estimates systolic/diastolic blood pressure from the wrist PPG signal alone.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Arduino-based smart door lock combining infrared sensors for intrusion/suspicious-activity detection with password-based unlocking; hardware+software system where incorrect password entry or forced door opening triggers an alert to the homeowner.</t>
+          <t>Combining EDA, PPG and ST signals achieved the best stress-classification performance (macro F1-score 0.92, 94% accuracy) versus EDA alone (F1 0.83, 84% accuracy), confirming that multimodal sensor fusion improves stress detection; for blood pressure, an AdaBoost regressor with decision-tree base estimator performed best (up to 97%/96% accuracy for SBP/DBP), estimating blood pressure from PPG alone without needing additional ECG hardware. The wristband proved power-efficient (minimal battery drain over 1.5 hours active use, ~20-30 hours battery life), demonstrating feasibility for continuous unobtrusive monitoring in a smart home.</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Relevant as a low-cost door-security precedent for SmartBuild's home-safety scope - explicitly frames the security use case around protecting senior citizens left alone at home, useful when discussing complementary safety layers (entry security) alongside your core BLE health/occupancy monitoring.</t>
+          <t>Smart wristband with EDA/PPG/ST sensors streaming via BLE to a companion smartphone app then WiFi to a smart-home cloud; stress-detection model trained on ground-truth salivary cortisol (a clinically validated stress biomarker) using multiple sensor-combination feature sets; separate PPG-only blood-pressure estimation framework using signal decomposition (Fourier transform, derivatives) and regression models (MLP, Decision Tree, AdaBoost variants) validated on the MIMIC physiological database; also includes an indoor location detection component for the smart home.</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care use-case precedent within the household system - a BLE wristband combining stress, blood pressure and indoor-location monitoring is architecturally close to the system's health-monitoring module; its cortisol-validated stress model and low-power design support both the elderly-care use case and the report's general power-budget justification.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="160" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>2006.06442v1.pdf</t>
+          <t>igaa057.1318.pdf</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -2584,44 +2670,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Smart Motion Detection System Using Raspberry Pi</t>
+          <t>GSA 2020 Annual Scientific Meeting Abstracts (Innovation in Aging, Vol 4, Suppl 1) - including 'In-Home Resourcefulness' / Grandfamilies Support-Group Study and 'A Systematic Review of In-Home Smart Technology Adoption to Improve Older Adult Health and Family Caregiving'</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Venkat Margapuri</t>
+          <t>Multiple authors incl. (support-group/resourcefulness study authors); Geunhye Park; Erin Robinson (systematic review abstract), University of Missouri-Columbia; plus Hyun-E Yeom, Misook Jung, Eunyoung Park (Chungnam National University); Nadia Firdausya, Alex Bishop, Barbara Carlson, Weihua Sheng (Oklahoma State University)</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2006.06442v1, 2020. Kansas State University.</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>This paper throws light on the security issues that modern day homes and businesses face and describes the implementation of a motion detection system using Raspberry Pi which could be an effective solution to address the security concerns. The goal of the solution is to provide an implementation that uses PIR motion sensors for motion detection and sends notifications to users via emails. The system is formally modelled and verified using UPPAAL to ensure correctness of the state-machine behaviour (e.g., picture capture, video recording, email notification states).</t>
-        </is>
+          <t>Innovation in Aging, 2020, vol. 4, supplement 1, p. 409, Gerontological Society of America (GSA) 2020 Annual Scientific Meeting conference abstracts (poster session 'Technology II').</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>2020</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>The Raspberry Pi + PIR sensor motion-detection system is effective, low cost and low maintenance, with the added benefit of Raspberry Pi's high scalability and abundant built-in components for future enhancement. The authors highlight UPPAAL formal verification as a way to increase confidence in the correctness of the security system's state transitions before deployment.</t>
+          <t>This page compiles several conference abstracts. Most relevant is a study on grandparent caregivers ('grandfamilies') and support-group participation: of the sample, 53.8% (N=184) belonged to a support group (mostly online/Facebook), and knowing other families like their own affected self-appraised stress; grandmothers in support groups reported lower mindfulness, higher stress and worse mental health scores than non-participants, likely reflecting greater underlying need for support. An adjacent abstract, 'A Systematic Review of In-Home Smart Technology Adoption to Improve Older Adult Health and Family Caregiving' (Park &amp; Robinson), reviewed 1,227 identified articles (1991-2019) down to 48 included studies and found key facilitators of smart-technology adoption (technology familiarity, safety/security, personalised/non-obtrusive design, easy access, reduced caregiver burden) and barriers (cost, difficulty of use, time, stigma, privacy, data accuracy, confidence).</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Raspberry Pi-based motion detection using a PIR sensor, with states for idle/motion-detected/picture-capture/video-recording/email-notification; system correctness formally modelled and verified using the UPPAAL model-checking tool.</t>
+          <t>Both abstracts are systematic-review/survey findings rather than novel systems: the grandfamilies study highlights that caregiver support-group participation correlates with (but does not straightforwardly reduce) stress, suggesting unmet support needs among caregivers of higher burden; the smart-technology adoption review concludes that addressing the identified facilitators/barriers (especially non-obtrusive design, privacy and cost) is crucial for successful dissemination of in-home smart technologies among older adults and family caregivers.</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Low direct relevance to elderly health monitoring specifically, but useful as a low-cost hardware precedent (Raspberry Pi + PIR) for SmartBuild's motion/occupancy sensing layer, and its use of formal verification (UPPAAL) is a citable example if your report discusses reliability/correctness assurance for safety-critical smart-home logic.</t>
+          <t>Conference abstracts: (a) cross-sectional survey analysis of grandparent caregivers' support-group participation vs. mindfulness/stress/mental-health outcomes; (b) systematic literature review (Rew method, 1991-2019, Web of Science/PubMed/Scopus/CINAHL/PsycInfo, 1,227 -&gt; 48 articles) of facilitators/barriers to in-home internet-based smart technology adoption by older adults and family caregivers.</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care/caregiver adoption use case, retained per your instruction - grounds the household system's human-factors discussion for family caregivers; the facilitators/barriers list (non-obtrusive design, privacy, cost, stigma) is citable evidence for why the system as a whole (not just its elderly-care module) should favour unobtrusive, privacy-respecting design.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="160" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>A-Microphone-Array-System-for-Automatic-Fall-Detection.pdf</t>
+          <t>2006.06442v1.pdf</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -2631,44 +2720,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>A Microphone Array System for Automatic Fall Detection</t>
+          <t>Smart Motion Detection System Using Raspberry Pi</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Yun Li; K. C. Ho; Mihail Popescu</t>
+          <t>Venkat Margapuri</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Biomedical Engineering, vol. 59, no. 5, pp. 1291-1301, May 2012. University of Missouri.</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>More than a third of elderly fall each year in the United States. It has been shown that the longer the person lies on the floor, the poorer the outcome of medical intervention. To reduce delay of medical intervention, we have developed an acoustic fall detection system (acoustic-FADE) that automatically detects a fall and reports it promptly to the caregiver. Acoustic-FADE consists of a circular microphone array that captures the sounds in a room. When a sound is detected, acoustic-FADE locates the source, enhances the signal, and classifies it as 'fall' or 'nonfall.' The sound source is located using the steered response power with phase transform technique, robust under noisy environments and resilient to reverberation effects. Signal enhancement is performed by beamforming based on the estimated sound source location, with height information further improving classification.</t>
-        </is>
+          <t>arXiv:2006.06442v1, 2020. Kansas State University.</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>2020</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>By adding sound-source localization, estimated source height, and beamforming to prior single-microphone acoustic fall detection work, acoustic-FADE greatly increases specificity to 97% with sensitivity reaching 100% under clean acoustic conditions, a significant improvement over earlier single-microphone approaches (87% sensitivity at ~90% specificity). The authors note future work will target more challenging conditions (multiple interferences, heavy reverberation), improved classifiers accounting for temporal dynamics (e.g., hidden Markov models), and larger real elderly-fall datasets.</t>
+          <t>This paper throws light on the security issues that modern day homes and businesses face and describes the implementation of a motion detection system using Raspberry Pi which could be an effective solution to address the security concerns. The goal of the solution is to provide an implementation that uses PIR motion sensors for motion detection and sends notifications to users via emails. The system is formally modelled and verified using UPPAAL to ensure correctness of the state-machine behaviour (e.g., picture capture, video recording, email notification states).</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Circular 8-microphone array (25cm radius) for room-wide acoustic sensing; sound source localisation via steered response power with phase transform (SRP-PHAT), signal enhancement via beamforming, height estimation, and fall/non-fall classification; validated against real fall and non-fall acoustic data plus external experiments across varying acoustic environments and floor materials.</t>
+          <t>The Raspberry Pi + PIR sensor motion-detection system is effective, low cost and low maintenance, with the added benefit of Raspberry Pi's high scalability and abundant built-in components for future enhancement. The authors highlight UPPAAL formal verification as a way to increase confidence in the correctness of the security system's state transitions before deployment.</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Strong fit for SmartBuild's non-wearable, privacy-preserving fall-detection discussion - a foundational, highly-cited acoustic (non-camera, non-wearable) fall-detection approach useful for contrasting against your BLE wearable design, or for discussing hybrid ambient+wearable sensing coverage for residents who may not always wear a device.</t>
+          <t>Raspberry Pi-based motion detection using a PIR sensor, with states for idle/motion-detected/picture-capture/video-recording/email-notification; system correctness formally modelled and verified using the UPPAAL model-checking tool.</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Core household-security/motion-sensing component - a low-cost Raspberry Pi + PIR motion-detection system is general-purpose (not elderly-specific) and supports the report's motion/occupancy sensing layer; its use of formal verification (UPPAAL) is citable for discussing reliability assurance in the system's safety-critical logic generally.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="160" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>2208.10659v1.pdf</t>
+          <t>PID5934743.pdf</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -2678,44 +2770,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Fall Detection from Audios with Audio Transformers</t>
+          <t>Comparison of Zigbee, Z-Wave, Wi-Fi, and Bluetooth Wireless Technologies Used in Home Automation</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Prabhjot Kaur; Qifan Wang; Weisong Shi</t>
+          <t>Salim Jibrin Danbatta; Asaf Varol</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2208.10659v1 [cs.SD], 2022. Wayne State University + Meta AI.</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>Fall detection for the elderly is a well-researched problem with several proposed solutions, including wearable and non-wearable techniques. While the existing techniques have excellent detection rates, their adoption by the target population is lacking due to the need for wearing devices and user privacy concerns. Our paper investigates ambient sound input for fall detection among the elderly, especially targeting environments such as bathrooms where other sensing techniques (cameras, wearables) are often impractical or privacy-invasive. We develop and train a Transformer-based deep learning model to detect fall events from sound input, and additionally implement the solution on an autonomous mobile robot to provide broader sensing coverage.</t>
-        </is>
+          <t>Proceedings of the 2019 7th International Symposium on Digital Forensics and Security (ISDFS). Firat University, Turkey.</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>2019</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>The Transformer-based ambient-sound fall-detection model offers a non-wearable, non-intrusive and scalable solution particularly suited to privacy-sensitive spaces like bathrooms where cameras/wearables are impractical; deploying it on a mobile robot extends sensing coverage beyond fixed microphones. The authors plan to extend the solution to other indoor environments beyond the bathroom (with additional training) and to collect a greater variety of fall events and explore additional audio features to further improve results.</t>
+          <t>Most of the home automation wireless technologies on the internet of things are based on ZigBee, Z-Wave, Wi-Fi, and Bluetooth wireless technologies. While these solutions are good enough, users of smart homes are facing challenges of selecting the best technology. This paper compares the performance of ZigBee, Z-Wave, Wi-Fi and Bluetooth technologies from the user's perspective. Power consumption, range, cost, ease of use, scalability, and interoperability are the six indices developed as guidelines to potential users, and hence, the results of this study. With this knowledge, users can make the appropriate choice of wireless technology solution to use in their home automation systems.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Audio Spectrogram Transformer-style deep learning model trained on ambient sound recordings to classify fall vs. non-fall audio events; deployed both as a fixed sensor and on an autonomous mobile robot platform for extended room coverage.</t>
+          <t>No single protocol wins on every index: Bluetooth is the lowest-cost and lowest-power option but has the shortest range (10m) and is best for simple, low-node-count control; ZigBee offers a good range (100m) and moderate scalability but weaker cross-vendor interoperability; Z-Wave (30m range) is judged best for scalability and interoperability across many devices from different manufacturers due to its certified compatibility standard; Wi-Fi offers the longest range (up to 1000m) but at higher cost and power draw. The authors conclude protocol choice should be driven by the specific home-automation use case's priorities among these six indices.</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Directly relevant to SmartBuild's privacy-preserving sensing theme, particularly for bathrooms/private spaces where BLE wearables might be removed (e.g., during showering) - supports an argument for ambient audio as a complementary fall-detection layer to your wearable BLE system in exactly the rooms where wearable coverage gaps are most likely and most dangerous.</t>
+          <t>Comparative literature-based analysis of ZigBee, Z-Wave, Wi-Fi and Bluetooth across six user-relevant indices (power consumption, range, cost, ease of use, scalability, interoperability), including a device/technology mapping table (e.g., iPhone/Bluetooth+WiFi, Fitbit/Bluetooth, Samsung Smart TV/WiFi+Z-Wave).</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Core protocol-selection evidence for the household system's network design - its six-index comparison (power/range/cost/ease-of-use/scalability/interoperability) of ZigBee/Z-Wave/Wi-Fi/Bluetooth gives a ready-made framework for justifying BLE's fit for the household network as a whole, independent of elderly-specific needs.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="160" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Journal of Sensors - 2022 - De Raeve - Bluetooth%E2%80%90Low%E2%80%90Energy%E2%80%90Based Fall Detection and Warning System for Elderly People in.pdf</t>
+          <t>challenges-and-issues-in-multisensor-fusion-approach-for-17vbnje5m3.pdf</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -2725,44 +2820,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Bluetooth-Low-Energy-Based Fall Detection and Warning System for Elderly People in Nursing Homes</t>
+          <t>Challenges and Issues in Multisensor Fusion Approach for Fall Detection: Review Paper</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Nick De Raeve; Adnan Shahid; Matthias de Schepper; Eli De Poorter; Ingrid Moerman; Jo Verhaevert; Patrick Van Torre; Hendrik Rogier</t>
+          <t>Gregory Koshmak; Amy Loutfi; Maria Linden</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Hindawi Journal of Sensors, vol. 2022, Article ID 9930681, 14 pages. doi:10.1155/2022/9930681. IDLab, Ghent University-imec, Belgium.</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>Due to the ever growing population of elderly people, there is a dramatic increase in fall accidents. Currently, multiple ideas exist to prevent the elderly from falling, by means of technology or individualised fall prevention training programs. Most of them are costly, difficult to implement or less used by the elderly, and they do not deliver the required results. Furthermore, the increasingly older population will also impact the workload of medical and nursing personnel. Therefore, we propose a novel fall detection and warning system for nursing homes, relying on Bluetooth Low Energy wireless communication. This paper describes the hardware design of a fall-acceleration sensing wearable for the elderly, a novel algorithm for real-time filtering of the measurement data, and a strategy to confirm detected fall events based on changes in the person's orientation. We also compare the algorithm's performance to a machine learning procedure using a convolutional neural network.</t>
-        </is>
+          <t>Hindawi Journal of Sensors, vol. 2016, Article ID 6931789, 12 pages. Mälardalen University + Örebro University, Sweden.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>2016</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>The wearable's dual-confirmation approach (acceleration peak + orientation-change confirmation) makes a false confirmed fall alert virtually impossible, validated across three open-source databases (85 persons, 18,835 ADL/fall activities) achieving F1 scores of 82.94-89.8% for the rule-based algorithm, comparable to a CNN-based ML approach (86.72-95.09% F1). The unobtrusive wearable fits in a 32x23x10mm package, is energy-efficient via BLE and low-power accelerometer modes (e.g., during sleep), and provides excellent room coverage at low energy consumption - directly meeting the paper's design requirements for reliability and unobtrusiveness in a nursing-home deployment.</t>
+          <t>Emergency situations associated with falls are a serious concern for an aging society. Yet following recent development within ICT, a significant number of solutions have been proposed to track body movement and detect falls using various sensor technologies, thereby facilitating fall detection and in some cases prevention. A number of recent reviews on fall detection methods using ICT technologies have emerged in the literature and an increasingly popular approach considers combining information from several sensor sources to assess falls. The aim of this paper is to review in detail the subfield of fall detection techniques that explicitly considers the use of multisensor fusion based methods to assess and determine falls. The paper highlights key differences between the single sensor-based approach and a multifusion one, describes and categorizes the various systems used, provides information on the challenges of a multifusion approach, and finally discusses trends for future work.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>BLE-based wearable with a three-axis accelerometer: fall-peak detection via acceleration threshold (2.5g) plus a second independent confirmation signal from spatial-orientation change (60 degree threshold), 5ms sampling rate; validated via a dedicated measurement campaign (including harmless high-acceleration events like sitting down) and against three open-source fall-detection datasets; rule-based algorithm benchmarked against a CNN machine-learning alternative.</t>
+          <t>Multisensor fusion inherits most single-sensor fall-detection challenges (poor real-world performance vs. lab conditions, limited usability especially for wearables/smartphones, privacy concerns) plus fusion-specific problems: lack of a simplified/standardised evaluation procedure, added computational cost from processing multiple data streams (mitigated by staged preprocessing/filtering/feature-extraction pipelines), and difficulty integrating sensors with distinct technological backgrounds. The authors recommend building test environments that combine wearable, ambient and vision sensors, adding sensor types only as needed per patient/use-case to avoid data overload and unnecessary privacy violations.</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>One of the most directly relevant papers in your matrix - a BLE wearable fall-detection system explicitly targeting elderly nursing-home residents with a compact, unobtrusive form factor and dual-signal false-alarm rejection, making it a near-direct architectural precedent and benchmark (F1 82.9-95.1%) for SmartBuild's own BLE fall-detection design.</t>
+          <t>Structured literature review categorising multisensor fall-detection systems by sensor combination type (wearable+ambient, wearable+vision, etc.), summarising evaluation methodologies used across reviewed studies, and identifying and discussing recurring implementation and evaluation challenges.</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care use-case evidence for the household system's fall-detection component - its finding that sensor types should be added only per actual need (avoiding data overload/privacy violations) is a strong citable justification for keeping the system's overall multi-sensor design deliberately minimal and purposeful, applicable beyond fall detection alone.</t>
         </is>
       </c>
     </row>
     <row r="33" ht="160" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>2107.09509v1.pdf</t>
+          <t>A-Microphone-Array-System-for-Automatic-Fall-Detection.pdf</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -2772,37 +2870,40 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Wearable Health Monitoring System for Older Adults in a Smart Home Environment</t>
+          <t>A Microphone Array System for Automatic Fall Detection</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Rajdeep Kumar Nath; Himanshu Thapliyal</t>
+          <t>Yun Li; K. C. Ho; Mihail Popescu</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>arXiv:2107.09509v1 [eess.SP], 2021. University of Kentucky.</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>The advent of IoT has enabled the design of connected and integrated smart health monitoring systems. These smart health monitoring systems could be realized in a smart home context to render long-term care to the elderly population. In this paper, we present the design of a wearable health monitoring system suitable for older adults in a smart home context. The proposed system offers solutions to monitor the stress, blood pressure, and location of an individual within a smart home environment. The stress detection model uses electrodermal activity (EDA), photoplethysmography (PPG) and skin temperature (ST) signals from a smart wristband, transmitted via low-energy Bluetooth to a companion app and then to the smart-home cloud via WiFi; a separate framework estimates systolic/diastolic blood pressure from the wrist PPG signal alone.</t>
-        </is>
+          <t>IEEE Transactions on Biomedical Engineering, vol. 59, no. 5, pp. 1291-1301, May 2012. University of Missouri.</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>2012</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Combining EDA, PPG and ST signals achieved the best stress-classification performance (macro F1-score 0.92, 94% accuracy) versus EDA alone (F1 0.83, 84% accuracy), confirming that multimodal sensor fusion improves stress detection; for blood pressure, an AdaBoost regressor with decision-tree base estimator performed best (up to 97%/96% accuracy for SBP/DBP), estimating blood pressure from PPG alone without needing additional ECG hardware. The wristband proved power-efficient (minimal battery drain over 1.5 hours active use, ~20-30 hours battery life), demonstrating feasibility for continuous unobtrusive monitoring in a smart home.</t>
+          <t>More than a third of elderly fall each year in the United States. It has been shown that the longer the person lies on the floor, the poorer the outcome of medical intervention. To reduce delay of medical intervention, we have developed an acoustic fall detection system (acoustic-FADE) that automatically detects a fall and reports it promptly to the caregiver. Acoustic-FADE consists of a circular microphone array that captures the sounds in a room. When a sound is detected, acoustic-FADE locates the source, enhances the signal, and classifies it as 'fall' or 'nonfall.' The sound source is located using the steered response power with phase transform technique, robust under noisy environments and resilient to reverberation effects. Signal enhancement is performed by beamforming based on the estimated sound source location, with height information further improving classification.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Smart wristband with EDA/PPG/ST sensors streaming via BLE to a companion smartphone app then WiFi to a smart-home cloud; stress-detection model trained on ground-truth salivary cortisol (a clinically validated stress biomarker) using multiple sensor-combination feature sets; separate PPG-only blood-pressure estimation framework using signal decomposition (Fourier transform, derivatives) and regression models (MLP, Decision Tree, AdaBoost variants) validated on the MIMIC physiological database; also includes an indoor location detection component for the smart home.</t>
+          <t>By adding sound-source localization, estimated source height, and beamforming to prior single-microphone acoustic fall detection work, acoustic-FADE greatly increases specificity to 97% with sensitivity reaching 100% under clean acoustic conditions, a significant improvement over earlier single-microphone approaches (87% sensitivity at ~90% specificity). The authors note future work will target more challenging conditions (multiple interferences, heavy reverberation), improved classifiers accounting for temporal dynamics (e.g., hidden Markov models), and larger real elderly-fall datasets.</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Excellent direct match for SmartBuild - a BLE wristband combining stress, blood pressure and indoor location monitoring for older adults in a smart home is architecturally very close to your own system, and its cortisol-validated stress model plus low-power, all-day-battery design are strong citable precedents for both your sensor-fusion approach and your power-budget justification.</t>
+          <t>Circular 8-microphone array (25cm radius) for room-wide acoustic sensing; sound source localisation via steered response power with phase transform (SRP-PHAT), signal enhancement via beamforming, height estimation, and fall/non-fall classification; validated against real fall and non-fall acoustic data plus external experiments across varying acoustic environments and floor materials.</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Elderly-care use-case precedent for non-wearable, privacy-preserving fall detection - a foundational acoustic sensing approach useful for contrasting against the household system's BLE wearable design, and for discussing hybrid ambient+wearable sensing coverage as a general household design principle, not only for elderly residents.</t>
         </is>
       </c>
     </row>
